--- a/reports/pdf_rolling5_20261027.xlsx
+++ b/reports/pdf_rolling5_20261027.xlsx
@@ -536,7 +536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K130"/>
+  <dimension ref="A1:K160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -562,14 +562,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>최근 5거래일 변화  ·  2026-10-20 ~ 2026-10-27  (최근 5거래일)  ·  캡처 6/10  ·  대기: RISE, TIGER, TIGER, MIDAS</t>
+          <t>최근 5거래일 변화  ·  2026-10-20 ~ 2026-10-27  (최근 5거래일)  ·  캡처 9/10  ·  대기: RISE</t>
         </is>
       </c>
     </row>
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,331억   ·   현금 7억(0.2%)      오늘 2026-10-27  vs  5일전 2026-10-20      매수 17종목  /  매도 12종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,121억      오늘 2026-10-27  vs  5일전 2026-10-20      매수 17종목  /  매도 12종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -665,7 +665,7 @@
         <v>458</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>4120031761</v>
+        <v>4115886280</v>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
@@ -686,7 +686,7 @@
         <v>-95</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>-1143547622</v>
+        <v>-1142397011</v>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         <v>170</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>4706094326</v>
+        <v>4701359163</v>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>-82</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>-4808973355</v>
+        <v>-4804134677</v>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
@@ -753,7 +753,7 @@
         <v>158</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>2940014268</v>
+        <v>2937056094</v>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
@@ -774,7 +774,7 @@
         <v>-72</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-669876669</v>
+        <v>-669202654</v>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>113</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>6907804946</v>
+        <v>6900854473</v>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
@@ -818,7 +818,7 @@
         <v>-69</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-2921764423</v>
+        <v>-2918824612</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
@@ -834,23 +834,23 @@
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>프로티나  (신규)</t>
+          <t>에코프로에이치엔</t>
         </is>
       </c>
       <c r="B10" s="11" t="n">
         <v>104</v>
       </c>
       <c r="C10" s="11" t="n">
-        <v>4817322957</v>
+        <v>2308129525</v>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
-          <t>0.00%→1.17%</t>
+          <t>0.22%→0.77%</t>
         </is>
       </c>
       <c r="E10" s="13" t="inlineStr">
         <is>
-          <t>0→104</t>
+          <t>38→142</t>
         </is>
       </c>
       <c r="G10" s="14" t="inlineStr">
@@ -862,7 +862,7 @@
         <v>-46</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-2299917848</v>
+        <v>-2297603724</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
@@ -878,23 +878,23 @@
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>에코프로에이치엔</t>
+          <t>프로티나  (신규)</t>
         </is>
       </c>
       <c r="B11" s="11" t="n">
         <v>104</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>2310454251</v>
+        <v>4812475878</v>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>0.22%→0.77%</t>
+          <t>0.00%→1.17%</t>
         </is>
       </c>
       <c r="E11" s="13" t="inlineStr">
         <is>
-          <t>38→142</t>
+          <t>0→104</t>
         </is>
       </c>
       <c r="G11" s="14" t="inlineStr">
@@ -906,7 +906,7 @@
         <v>-33</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-869253245</v>
+        <v>-868378622</v>
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>76</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>2149227405</v>
+        <v>2147064903</v>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
@@ -950,7 +950,7 @@
         <v>-32</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>-289134801</v>
+        <v>-288843881</v>
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         <v>63</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>747706891</v>
+        <v>746954565</v>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>-16</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>-3832865080</v>
+        <v>-3829008540</v>
       </c>
       <c r="J13" s="16" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>29</v>
       </c>
       <c r="C14" s="11" t="n">
-        <v>1176101131</v>
+        <v>1174917766</v>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
         <v>-11</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>-1537320833</v>
+        <v>-1535774017</v>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
@@ -1061,7 +1061,7 @@
         <v>29</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>412788436</v>
+        <v>412373098</v>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>-6</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-114508832</v>
+        <v>-114393616</v>
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
         <v>25</v>
       </c>
       <c r="C16" s="11" t="n">
-        <v>1221377844</v>
+        <v>1220148922</v>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>-5</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>-1041215293</v>
+        <v>-1040167647</v>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>15</v>
       </c>
       <c r="C17" s="11" t="n">
-        <v>1206219340</v>
+        <v>1205005670</v>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
@@ -1170,7 +1170,7 @@
         <v>-4</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-792417023</v>
+        <v>-791619712</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
@@ -1186,23 +1186,23 @@
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>원익머트리얼즈</t>
+          <t>파두</t>
         </is>
       </c>
       <c r="B18" s="11" t="n">
         <v>12</v>
       </c>
       <c r="C18" s="11" t="n">
-        <v>393624111</v>
+        <v>533836875</v>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>1.43%→1.47%</t>
+          <t>0.42%→0.50%</t>
         </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
-          <t>173→185</t>
+          <t>34→46</t>
         </is>
       </c>
       <c r="G18" s="17" t="n"/>
@@ -1214,23 +1214,23 @@
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>파크시스템스</t>
+          <t>원익머트리얼즈</t>
         </is>
       </c>
       <c r="B19" s="11" t="n">
         <v>12</v>
       </c>
       <c r="C19" s="11" t="n">
-        <v>2659944749</v>
+        <v>393228055</v>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>1.43%→1.99%</t>
+          <t>1.43%→1.47%</t>
         </is>
       </c>
       <c r="E19" s="13" t="inlineStr">
         <is>
-          <t>25→37</t>
+          <t>173→185</t>
         </is>
       </c>
       <c r="G19" s="17" t="n"/>
@@ -1242,23 +1242,23 @@
     <row r="20">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>파두</t>
+          <t>파크시스템스</t>
         </is>
       </c>
       <c r="B20" s="11" t="n">
         <v>12</v>
       </c>
       <c r="C20" s="11" t="n">
-        <v>534374551</v>
+        <v>2657268375</v>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
-          <t>0.42%→0.50%</t>
+          <t>1.43%→1.99%</t>
         </is>
       </c>
       <c r="E20" s="13" t="inlineStr">
         <is>
-          <t>34→46</t>
+          <t>25→37</t>
         </is>
       </c>
       <c r="G20" s="17" t="n"/>
@@ -1277,7 +1277,7 @@
         <v>9</v>
       </c>
       <c r="C21" s="11" t="n">
-        <v>1954701551</v>
+        <v>1952734775</v>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>8</v>
       </c>
       <c r="C22" s="11" t="n">
-        <v>764187415</v>
+        <v>763418508</v>
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
     <row r="24" ht="19" customHeight="1">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,109억   ·   현금 62억(2.1%)      오늘 2026-10-27  vs  5일전 2026-10-20      매수 8종목  /  매도 16종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 2,996억      오늘 2026-10-27  vs  5일전 2026-10-20      매수 8종목  /  매도 16종목</t>
         </is>
       </c>
       <c r="B24" s="4" t="n"/>
@@ -1422,7 +1422,7 @@
         <v>141</v>
       </c>
       <c r="C27" s="11" t="n">
-        <v>3422408527</v>
+        <v>3422407125</v>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
@@ -1443,7 +1443,7 @@
         <v>-118</v>
       </c>
       <c r="I27" s="15" t="n">
-        <v>-1444744854</v>
+        <v>-1444744262</v>
       </c>
       <c r="J27" s="16" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
         <v>104</v>
       </c>
       <c r="C28" s="11" t="n">
-        <v>4562781770</v>
+        <v>4562779901</v>
       </c>
       <c r="D28" s="12" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>-113</v>
       </c>
       <c r="I28" s="15" t="n">
-        <v>-2466682742</v>
+        <v>-2466681731</v>
       </c>
       <c r="J28" s="16" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
         <v>65</v>
       </c>
       <c r="C29" s="11" t="n">
-        <v>1424124053</v>
+        <v>1424123470</v>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>-58</v>
       </c>
       <c r="I29" s="15" t="n">
-        <v>-1200678345</v>
+        <v>-1200677853</v>
       </c>
       <c r="J29" s="16" t="inlineStr">
         <is>
@@ -1554,7 +1554,7 @@
         <v>39</v>
       </c>
       <c r="C30" s="11" t="n">
-        <v>1587479459</v>
+        <v>1587478809</v>
       </c>
       <c r="D30" s="12" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         <v>-43</v>
       </c>
       <c r="I30" s="15" t="n">
-        <v>-5045383688</v>
+        <v>-5045381621</v>
       </c>
       <c r="J30" s="16" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
         <v>13</v>
       </c>
       <c r="C31" s="11" t="n">
-        <v>904737634</v>
+        <v>904737263</v>
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
@@ -1619,7 +1619,7 @@
         <v>-38</v>
       </c>
       <c r="I31" s="15" t="n">
-        <v>-1961016673</v>
+        <v>-1961015870</v>
       </c>
       <c r="J31" s="16" t="inlineStr">
         <is>
@@ -1642,7 +1642,7 @@
         <v>12</v>
       </c>
       <c r="C32" s="11" t="n">
-        <v>9356688348</v>
+        <v>9356684515</v>
       </c>
       <c r="D32" s="12" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>-33</v>
       </c>
       <c r="I32" s="15" t="n">
-        <v>-1150092943</v>
+        <v>-1150092472</v>
       </c>
       <c r="J32" s="16" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
         <v>9</v>
       </c>
       <c r="C33" s="11" t="n">
-        <v>918270034</v>
+        <v>918269658</v>
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>-32</v>
       </c>
       <c r="I33" s="15" t="n">
-        <v>-3031257713</v>
+        <v>-3031256471</v>
       </c>
       <c r="J33" s="16" t="inlineStr">
         <is>
@@ -1730,7 +1730,7 @@
         <v>6</v>
       </c>
       <c r="C34" s="11" t="n">
-        <v>147084305</v>
+        <v>147084245</v>
       </c>
       <c r="D34" s="12" t="inlineStr">
         <is>
@@ -1751,7 +1751,7 @@
         <v>-26</v>
       </c>
       <c r="I34" s="15" t="n">
-        <v>-173128806</v>
+        <v>-173128736</v>
       </c>
       <c r="J34" s="16" t="inlineStr">
         <is>
@@ -1779,7 +1779,7 @@
         <v>-25</v>
       </c>
       <c r="I35" s="15" t="n">
-        <v>-286623761</v>
+        <v>-286623643</v>
       </c>
       <c r="J35" s="16" t="inlineStr">
         <is>
@@ -1807,7 +1807,7 @@
         <v>-24</v>
       </c>
       <c r="I36" s="15" t="n">
-        <v>-463968017</v>
+        <v>-463967827</v>
       </c>
       <c r="J36" s="16" t="inlineStr">
         <is>
@@ -1835,7 +1835,7 @@
         <v>-22</v>
       </c>
       <c r="I37" s="15" t="n">
-        <v>-2711313101</v>
+        <v>-2711311990</v>
       </c>
       <c r="J37" s="16" t="inlineStr">
         <is>
@@ -1863,7 +1863,7 @@
         <v>-22</v>
       </c>
       <c r="I38" s="15" t="n">
-        <v>-1045539039</v>
+        <v>-1045538611</v>
       </c>
       <c r="J38" s="16" t="inlineStr">
         <is>
@@ -1891,7 +1891,7 @@
         <v>-18</v>
       </c>
       <c r="I39" s="15" t="n">
-        <v>-143636765</v>
+        <v>-143636707</v>
       </c>
       <c r="J39" s="16" t="inlineStr">
         <is>
@@ -1919,7 +1919,7 @@
         <v>-7</v>
       </c>
       <c r="I40" s="15" t="n">
-        <v>-1325047549</v>
+        <v>-1325047007</v>
       </c>
       <c r="J40" s="16" t="inlineStr">
         <is>
@@ -1947,7 +1947,7 @@
         <v>-6</v>
       </c>
       <c r="I41" s="15" t="n">
-        <v>-26517061</v>
+        <v>-26517050</v>
       </c>
       <c r="J41" s="16" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         <v>-4</v>
       </c>
       <c r="I42" s="15" t="n">
-        <v>-58318202</v>
+        <v>-58318178</v>
       </c>
       <c r="J42" s="16" t="inlineStr">
         <is>
@@ -1991,7 +1991,7 @@
     <row r="44" ht="19" customHeight="1">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,181억   ·   현금 32억(1.6%)      오늘 2026-10-27  vs  5일전 2026-10-20      매수 21종목  /  매도 31종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,019억      오늘 2026-10-27  vs  5일전 2026-10-20      매수 21종목  /  매도 31종목</t>
         </is>
       </c>
       <c r="B44" s="4" t="n"/>
@@ -2087,7 +2087,7 @@
         <v>995</v>
       </c>
       <c r="C47" s="11" t="n">
-        <v>6172983367</v>
+        <v>6191681511</v>
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>-249</v>
       </c>
       <c r="I47" s="15" t="n">
-        <v>-7378870025</v>
+        <v>-7401220834</v>
       </c>
       <c r="J47" s="16" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>494</v>
       </c>
       <c r="C48" s="11" t="n">
-        <v>9080218953</v>
+        <v>9107723196</v>
       </c>
       <c r="D48" s="12" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
         <v>-202</v>
       </c>
       <c r="I48" s="15" t="n">
-        <v>-1191881450</v>
+        <v>-1195491693</v>
       </c>
       <c r="J48" s="16" t="inlineStr">
         <is>
@@ -2175,7 +2175,7 @@
         <v>278</v>
       </c>
       <c r="C49" s="11" t="n">
-        <v>9999665454</v>
+        <v>10029954728</v>
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
         <v>-130</v>
       </c>
       <c r="I49" s="15" t="n">
-        <v>-4453022429</v>
+        <v>-4466510761</v>
       </c>
       <c r="J49" s="16" t="inlineStr">
         <is>
@@ -2219,7 +2219,7 @@
         <v>248</v>
       </c>
       <c r="C50" s="11" t="n">
-        <v>5352338919</v>
+        <v>5368551307</v>
       </c>
       <c r="D50" s="12" t="inlineStr">
         <is>
@@ -2240,7 +2240,7 @@
         <v>-121</v>
       </c>
       <c r="I50" s="15" t="n">
-        <v>-1046166571</v>
+        <v>-1049335439</v>
       </c>
       <c r="J50" s="16" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>199</v>
       </c>
       <c r="C51" s="11" t="n">
-        <v>10073783495</v>
+        <v>10104297274</v>
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
@@ -2284,7 +2284,7 @@
         <v>-118</v>
       </c>
       <c r="I51" s="15" t="n">
-        <v>-1105896603</v>
+        <v>-1109246396</v>
       </c>
       <c r="J51" s="16" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         <v>151</v>
       </c>
       <c r="C52" s="11" t="n">
-        <v>1333451527</v>
+        <v>1337490590</v>
       </c>
       <c r="D52" s="12" t="inlineStr">
         <is>
@@ -2321,23 +2321,23 @@
       </c>
       <c r="G52" s="14" t="inlineStr">
         <is>
-          <t>한선엔지니어링</t>
+          <t>필옵틱스</t>
         </is>
       </c>
       <c r="H52" s="15" t="n">
         <v>-112</v>
       </c>
       <c r="I52" s="15" t="n">
-        <v>-945437316</v>
+        <v>-2061201705</v>
       </c>
       <c r="J52" s="16" t="inlineStr">
         <is>
-          <t>1.01%→0.43%</t>
+          <t>2.12%→1.00%</t>
         </is>
       </c>
       <c r="K52" s="13" t="inlineStr">
         <is>
-          <t>213→101</t>
+          <t>220→108</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
         <v>150</v>
       </c>
       <c r="C53" s="11" t="n">
-        <v>3578851952</v>
+        <v>3589692397</v>
       </c>
       <c r="D53" s="12" t="inlineStr">
         <is>
@@ -2365,23 +2365,23 @@
       </c>
       <c r="G53" s="14" t="inlineStr">
         <is>
-          <t>필옵틱스</t>
+          <t>한선엔지니어링</t>
         </is>
       </c>
       <c r="H53" s="15" t="n">
         <v>-112</v>
       </c>
       <c r="I53" s="15" t="n">
-        <v>-2054977121</v>
+        <v>-948301072</v>
       </c>
       <c r="J53" s="16" t="inlineStr">
         <is>
-          <t>2.12%→1.00%</t>
+          <t>1.01%→0.43%</t>
         </is>
       </c>
       <c r="K53" s="13" t="inlineStr">
         <is>
-          <t>220→108</t>
+          <t>213→101</t>
         </is>
       </c>
     </row>
@@ -2395,7 +2395,7 @@
         <v>149</v>
       </c>
       <c r="C54" s="11" t="n">
-        <v>3146881716</v>
+        <v>3156413711</v>
       </c>
       <c r="D54" s="12" t="inlineStr">
         <is>
@@ -2416,7 +2416,7 @@
         <v>-108</v>
       </c>
       <c r="I54" s="15" t="n">
-        <v>-2402137310</v>
+        <v>-2409413453</v>
       </c>
       <c r="J54" s="16" t="inlineStr">
         <is>
@@ -2439,7 +2439,7 @@
         <v>139</v>
       </c>
       <c r="C55" s="11" t="n">
-        <v>2284327246</v>
+        <v>2291246539</v>
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
@@ -2460,7 +2460,7 @@
         <v>-106</v>
       </c>
       <c r="I55" s="15" t="n">
-        <v>-7359796014</v>
+        <v>-7382089047</v>
       </c>
       <c r="J55" s="16" t="inlineStr">
         <is>
@@ -2483,7 +2483,7 @@
         <v>134</v>
       </c>
       <c r="C56" s="11" t="n">
-        <v>1786488974</v>
+        <v>1791900301</v>
       </c>
       <c r="D56" s="12" t="inlineStr">
         <is>
@@ -2504,7 +2504,7 @@
         <v>-100</v>
       </c>
       <c r="I56" s="15" t="n">
-        <v>-1923901049</v>
+        <v>-1929728601</v>
       </c>
       <c r="J56" s="16" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         <v>99</v>
       </c>
       <c r="C57" s="11" t="n">
-        <v>2097415144</v>
+        <v>2103768275</v>
       </c>
       <c r="D57" s="12" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
         <v>-97</v>
       </c>
       <c r="I57" s="15" t="n">
-        <v>-1754148957</v>
+        <v>-1759462324</v>
       </c>
       <c r="J57" s="16" t="inlineStr">
         <is>
@@ -2571,7 +2571,7 @@
         <v>99</v>
       </c>
       <c r="C58" s="11" t="n">
-        <v>1607364877</v>
+        <v>1612233631</v>
       </c>
       <c r="D58" s="12" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>-74</v>
       </c>
       <c r="I58" s="15" t="n">
-        <v>-2993893633</v>
+        <v>-3002962223</v>
       </c>
       <c r="J58" s="16" t="inlineStr">
         <is>
@@ -2615,7 +2615,7 @@
         <v>79</v>
       </c>
       <c r="C59" s="11" t="n">
-        <v>5380850935</v>
+        <v>5397149687</v>
       </c>
       <c r="D59" s="12" t="inlineStr">
         <is>
@@ -2636,7 +2636,7 @@
         <v>-70</v>
       </c>
       <c r="I59" s="15" t="n">
-        <v>-7743124224</v>
+        <v>-7766578369</v>
       </c>
       <c r="J59" s="16" t="inlineStr">
         <is>
@@ -2659,7 +2659,7 @@
         <v>70</v>
       </c>
       <c r="C60" s="11" t="n">
-        <v>2196811198</v>
+        <v>2203465402</v>
       </c>
       <c r="D60" s="12" t="inlineStr">
         <is>
@@ -2680,7 +2680,7 @@
         <v>-66</v>
       </c>
       <c r="I60" s="15" t="n">
-        <v>-1690128922</v>
+        <v>-1695248371</v>
       </c>
       <c r="J60" s="16" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         <v>50</v>
       </c>
       <c r="C61" s="11" t="n">
-        <v>2263801235</v>
+        <v>2270658354</v>
       </c>
       <c r="D61" s="12" t="inlineStr">
         <is>
@@ -2717,23 +2717,23 @@
       </c>
       <c r="G61" s="14" t="inlineStr">
         <is>
-          <t>두산테스나</t>
+          <t>비츠로셀  (편출)</t>
         </is>
       </c>
       <c r="H61" s="15" t="n">
         <v>-50</v>
       </c>
       <c r="I61" s="15" t="n">
-        <v>-3148201717</v>
+        <v>-835774394</v>
       </c>
       <c r="J61" s="16" t="inlineStr">
         <is>
-          <t>2.73%→1.24%</t>
+          <t>0.35%→0.00%</t>
         </is>
       </c>
       <c r="K61" s="13" t="inlineStr">
         <is>
-          <t>89→39</t>
+          <t>50→0</t>
         </is>
       </c>
     </row>
@@ -2747,7 +2747,7 @@
         <v>40</v>
       </c>
       <c r="C62" s="11" t="n">
-        <v>2832721545</v>
+        <v>2841301940</v>
       </c>
       <c r="D62" s="12" t="inlineStr">
         <is>
@@ -2761,23 +2761,23 @@
       </c>
       <c r="G62" s="14" t="inlineStr">
         <is>
-          <t>비츠로셀  (편출)</t>
+          <t>두산테스나</t>
         </is>
       </c>
       <c r="H62" s="15" t="n">
         <v>-50</v>
       </c>
       <c r="I62" s="15" t="n">
-        <v>-833250454</v>
+        <v>-3157737710</v>
       </c>
       <c r="J62" s="16" t="inlineStr">
         <is>
-          <t>0.35%→0.00%</t>
+          <t>2.73%→1.24%</t>
         </is>
       </c>
       <c r="K62" s="13" t="inlineStr">
         <is>
-          <t>50→0</t>
+          <t>89→39</t>
         </is>
       </c>
     </row>
@@ -2791,7 +2791,7 @@
         <v>27</v>
       </c>
       <c r="C63" s="11" t="n">
-        <v>625482341</v>
+        <v>627376945</v>
       </c>
       <c r="D63" s="12" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>-44</v>
       </c>
       <c r="I63" s="15" t="n">
-        <v>-2024089104</v>
+        <v>-2030220128</v>
       </c>
       <c r="J63" s="16" t="inlineStr">
         <is>
@@ -2835,7 +2835,7 @@
         <v>20</v>
       </c>
       <c r="C64" s="11" t="n">
-        <v>1037520566</v>
+        <v>1040663245</v>
       </c>
       <c r="D64" s="12" t="inlineStr">
         <is>
@@ -2856,7 +2856,7 @@
         <v>-39</v>
       </c>
       <c r="I64" s="15" t="n">
-        <v>-2301157255</v>
+        <v>-2308127526</v>
       </c>
       <c r="J64" s="16" t="inlineStr">
         <is>
@@ -2879,7 +2879,7 @@
         <v>16</v>
       </c>
       <c r="C65" s="11" t="n">
-        <v>2307361259</v>
+        <v>2314350322</v>
       </c>
       <c r="D65" s="12" t="inlineStr">
         <is>
@@ -2900,7 +2900,7 @@
         <v>-35</v>
       </c>
       <c r="I65" s="15" t="n">
-        <v>-8754904775</v>
+        <v>-8781423633</v>
       </c>
       <c r="J65" s="16" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>15</v>
       </c>
       <c r="C66" s="11" t="n">
-        <v>959310523</v>
+        <v>962216302</v>
       </c>
       <c r="D66" s="12" t="inlineStr">
         <is>
@@ -2944,7 +2944,7 @@
         <v>-28</v>
       </c>
       <c r="I66" s="15" t="n">
-        <v>-1849849009</v>
+        <v>-1855452255</v>
       </c>
       <c r="J66" s="16" t="inlineStr">
         <is>
@@ -2967,7 +2967,7 @@
         <v>6</v>
       </c>
       <c r="C67" s="11" t="n">
-        <v>431640235</v>
+        <v>432947686</v>
       </c>
       <c r="D67" s="12" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
         <v>-26</v>
       </c>
       <c r="I67" s="15" t="n">
-        <v>-4135562256</v>
+        <v>-4148088992</v>
       </c>
       <c r="J67" s="16" t="inlineStr">
         <is>
@@ -3016,7 +3016,7 @@
         <v>-26</v>
       </c>
       <c r="I68" s="15" t="n">
-        <v>-1575288859</v>
+        <v>-1580060454</v>
       </c>
       <c r="J68" s="16" t="inlineStr">
         <is>
@@ -3044,7 +3044,7 @@
         <v>-25</v>
       </c>
       <c r="I69" s="15" t="n">
-        <v>-769725420</v>
+        <v>-772056940</v>
       </c>
       <c r="J69" s="16" t="inlineStr">
         <is>
@@ -3072,7 +3072,7 @@
         <v>-25</v>
       </c>
       <c r="I70" s="15" t="n">
-        <v>-1070850584</v>
+        <v>-1074094221</v>
       </c>
       <c r="J70" s="16" t="inlineStr">
         <is>
@@ -3100,7 +3100,7 @@
         <v>-19</v>
       </c>
       <c r="I71" s="15" t="n">
-        <v>-3197701744</v>
+        <v>-3207387674</v>
       </c>
       <c r="J71" s="16" t="inlineStr">
         <is>
@@ -3128,7 +3128,7 @@
         <v>-15</v>
       </c>
       <c r="I72" s="15" t="n">
-        <v>-1391940759</v>
+        <v>-1396156988</v>
       </c>
       <c r="J72" s="16" t="inlineStr">
         <is>
@@ -3156,7 +3156,7 @@
         <v>-9</v>
       </c>
       <c r="I73" s="15" t="n">
-        <v>-1464210799</v>
+        <v>-1468645935</v>
       </c>
       <c r="J73" s="16" t="inlineStr">
         <is>
@@ -3184,7 +3184,7 @@
         <v>-8</v>
       </c>
       <c r="I74" s="15" t="n">
-        <v>-1834801001</v>
+        <v>-1840358666</v>
       </c>
       <c r="J74" s="16" t="inlineStr">
         <is>
@@ -3212,7 +3212,7 @@
         <v>-8</v>
       </c>
       <c r="I75" s="15" t="n">
-        <v>-695376379</v>
+        <v>-697482694</v>
       </c>
       <c r="J75" s="16" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         <v>-7</v>
       </c>
       <c r="I76" s="15" t="n">
-        <v>-1282050699</v>
+        <v>-1285934068</v>
       </c>
       <c r="J76" s="16" t="inlineStr">
         <is>
@@ -3268,7 +3268,7 @@
         <v>-5</v>
       </c>
       <c r="I77" s="15" t="n">
-        <v>-520410284</v>
+        <v>-521986622</v>
       </c>
       <c r="J77" s="16" t="inlineStr">
         <is>
@@ -3284,7 +3284,7 @@
     <row r="79" ht="19" customHeight="1">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,148억   ·   현금 1억(0.0%)      오늘 2026-10-27  vs  5일전 2026-10-20      매수 5종목  /  매도 3종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,079억      오늘 2026-10-27  vs  5일전 2026-10-20      매수 5종목  /  매도 3종목</t>
         </is>
       </c>
       <c r="B79" s="4" t="n"/>
@@ -3380,7 +3380,7 @@
         <v>209</v>
       </c>
       <c r="C82" s="11" t="n">
-        <v>1929363364</v>
+        <v>1929363460</v>
       </c>
       <c r="D82" s="12" t="inlineStr">
         <is>
@@ -3401,7 +3401,7 @@
         <v>-389</v>
       </c>
       <c r="I82" s="15" t="n">
-        <v>-3646020644</v>
+        <v>-3646020824</v>
       </c>
       <c r="J82" s="16" t="inlineStr">
         <is>
@@ -3424,7 +3424,7 @@
         <v>104</v>
       </c>
       <c r="C83" s="11" t="n">
-        <v>4037739199</v>
+        <v>4037739399</v>
       </c>
       <c r="D83" s="12" t="inlineStr">
         <is>
@@ -3445,7 +3445,7 @@
         <v>-303</v>
       </c>
       <c r="I83" s="15" t="n">
-        <v>-4718984469</v>
+        <v>-4718984703</v>
       </c>
       <c r="J83" s="16" t="inlineStr">
         <is>
@@ -3468,7 +3468,7 @@
         <v>14</v>
       </c>
       <c r="C84" s="11" t="n">
-        <v>1993740790</v>
+        <v>1993740888</v>
       </c>
       <c r="D84" s="12" t="inlineStr">
         <is>
@@ -3489,7 +3489,7 @@
         <v>-62</v>
       </c>
       <c r="I84" s="15" t="n">
-        <v>-1018201603</v>
+        <v>-1018201654</v>
       </c>
       <c r="J84" s="16" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
         <v>9</v>
       </c>
       <c r="C85" s="11" t="n">
-        <v>5279474091</v>
+        <v>5279474352</v>
       </c>
       <c r="D85" s="12" t="inlineStr">
         <is>
@@ -3540,7 +3540,7 @@
         <v>7</v>
       </c>
       <c r="C86" s="11" t="n">
-        <v>537320213</v>
+        <v>537320239</v>
       </c>
       <c r="D86" s="12" t="inlineStr">
         <is>
@@ -3561,7 +3561,7 @@
     <row r="88" ht="19" customHeight="1">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 243억   ·   현금 2억(0.9%)      오늘 2026-10-27  vs  5일전 2026-10-20      매수 11종목  /  매도 8종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 233억      오늘 2026-10-27  vs  5일전 2026-10-20      매수 11종목  /  매도 8종목</t>
         </is>
       </c>
       <c r="B88" s="4" t="n"/>
@@ -3657,11 +3657,11 @@
         <v>345</v>
       </c>
       <c r="C91" s="11" t="n">
-        <v>177743889</v>
+        <v>170457600</v>
       </c>
       <c r="D91" s="12" t="inlineStr">
         <is>
-          <t>6.56%→7.26%</t>
+          <t>6.59%→7.29%</t>
         </is>
       </c>
       <c r="E91" s="13" t="inlineStr">
@@ -3678,11 +3678,11 @@
         <v>-86</v>
       </c>
       <c r="I91" s="15" t="n">
-        <v>-130444718</v>
+        <v>-153286400</v>
       </c>
       <c r="J91" s="16" t="inlineStr">
         <is>
-          <t>5.38%→4.81%</t>
+          <t>6.62%→5.92%</t>
         </is>
       </c>
       <c r="K91" s="13" t="inlineStr">
@@ -3701,11 +3701,11 @@
         <v>77</v>
       </c>
       <c r="C92" s="11" t="n">
-        <v>74412753</v>
+        <v>71800960</v>
       </c>
       <c r="D92" s="12" t="inlineStr">
         <is>
-          <t>3.27%→3.56%</t>
+          <t>3.30%→3.60%</t>
         </is>
       </c>
       <c r="E92" s="13" t="inlineStr">
@@ -3722,11 +3722,11 @@
         <v>-26</v>
       </c>
       <c r="I92" s="15" t="n">
-        <v>-76377552</v>
+        <v>-68972800</v>
       </c>
       <c r="J92" s="16" t="inlineStr">
         <is>
-          <t>3.16%→2.82%</t>
+          <t>2.99%→2.67%</t>
         </is>
       </c>
       <c r="K92" s="13" t="inlineStr">
@@ -3745,11 +3745,11 @@
         <v>61</v>
       </c>
       <c r="C93" s="11" t="n">
-        <v>97599939</v>
+        <v>90182400</v>
       </c>
       <c r="D93" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.40%</t>
+          <t>0.00%→0.39%</t>
         </is>
       </c>
       <c r="E93" s="13" t="inlineStr">
@@ -3766,11 +3766,11 @@
         <v>-24</v>
       </c>
       <c r="I93" s="15" t="n">
-        <v>-86169546</v>
+        <v>-79718400</v>
       </c>
       <c r="J93" s="16" t="inlineStr">
         <is>
-          <t>4.77%→4.39%</t>
+          <t>4.62%→4.25%</t>
         </is>
       </c>
       <c r="K93" s="13" t="inlineStr">
@@ -3789,11 +3789,11 @@
         <v>34</v>
       </c>
       <c r="C94" s="11" t="n">
-        <v>28157422</v>
+        <v>25981440</v>
       </c>
       <c r="D94" s="12" t="inlineStr">
         <is>
-          <t>0.31%→0.42%</t>
+          <t>0.30%→0.41%</t>
         </is>
       </c>
       <c r="E94" s="13" t="inlineStr">
@@ -3810,7 +3810,7 @@
         <v>-22</v>
       </c>
       <c r="I94" s="15" t="n">
-        <v>-40972774</v>
+        <v>-39142400</v>
       </c>
       <c r="J94" s="16" t="inlineStr">
         <is>
@@ -3833,11 +3833,11 @@
         <v>24</v>
       </c>
       <c r="C95" s="11" t="n">
-        <v>46463971</v>
+        <v>44851200</v>
       </c>
       <c r="D95" s="12" t="inlineStr">
         <is>
-          <t>1.27%→1.46%</t>
+          <t>1.29%→1.48%</t>
         </is>
       </c>
       <c r="E95" s="13" t="inlineStr">
@@ -3854,11 +3854,11 @@
         <v>-15</v>
       </c>
       <c r="I95" s="15" t="n">
-        <v>-67103958</v>
+        <v>-52320000</v>
       </c>
       <c r="J95" s="16" t="inlineStr">
         <is>
-          <t>1.68%→1.39%</t>
+          <t>1.37%→1.14%</t>
         </is>
       </c>
       <c r="K95" s="13" t="inlineStr">
@@ -3877,11 +3877,11 @@
         <v>11</v>
       </c>
       <c r="C96" s="11" t="n">
-        <v>23372785</v>
+        <v>22070400</v>
       </c>
       <c r="D96" s="12" t="inlineStr">
         <is>
-          <t>7.48%→7.54%</t>
+          <t>7.40%→7.45%</t>
         </is>
       </c>
       <c r="E96" s="13" t="inlineStr">
@@ -3898,11 +3898,11 @@
         <v>-8</v>
       </c>
       <c r="I96" s="15" t="n">
-        <v>-61183962</v>
+        <v>-52838400</v>
       </c>
       <c r="J96" s="16" t="inlineStr">
         <is>
-          <t>1.59%→1.33%</t>
+          <t>1.44%→1.20%</t>
         </is>
       </c>
       <c r="K96" s="13" t="inlineStr">
@@ -3921,11 +3921,11 @@
         <v>10</v>
       </c>
       <c r="C97" s="11" t="n">
-        <v>39295975</v>
+        <v>37184000</v>
       </c>
       <c r="D97" s="12" t="inlineStr">
         <is>
-          <t>1.03%→1.19%</t>
+          <t>1.02%→1.18%</t>
         </is>
       </c>
       <c r="E97" s="13" t="inlineStr">
@@ -3942,11 +3942,11 @@
         <v>-6</v>
       </c>
       <c r="I97" s="15" t="n">
-        <v>-45119972</v>
+        <v>-41856000</v>
       </c>
       <c r="J97" s="16" t="inlineStr">
         <is>
-          <t>2.85%→2.65%</t>
+          <t>2.77%→2.57%</t>
         </is>
       </c>
       <c r="K97" s="13" t="inlineStr">
@@ -3958,23 +3958,23 @@
     <row r="98">
       <c r="A98" s="10" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>선익시스템</t>
         </is>
       </c>
       <c r="B98" s="11" t="n">
         <v>7</v>
       </c>
       <c r="C98" s="11" t="n">
-        <v>49369569</v>
+        <v>37004800</v>
       </c>
       <c r="D98" s="12" t="inlineStr">
         <is>
-          <t>2.26%→2.45%</t>
+          <t>1.34%→1.49%</t>
         </is>
       </c>
       <c r="E98" s="13" t="inlineStr">
         <is>
-          <t>77→84</t>
+          <t>58→65</t>
         </is>
       </c>
       <c r="G98" s="14" t="inlineStr">
@@ -3986,11 +3986,11 @@
         <v>-3</v>
       </c>
       <c r="I98" s="15" t="n">
-        <v>-7823995</v>
+        <v>-7804800</v>
       </c>
       <c r="J98" s="16" t="inlineStr">
         <is>
-          <t>0.14%→0.11%</t>
+          <t>0.15%→0.11%</t>
         </is>
       </c>
       <c r="K98" s="13" t="inlineStr">
@@ -4002,23 +4002,23 @@
     <row r="99">
       <c r="A99" s="10" t="inlineStr">
         <is>
-          <t>선익시스템</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="B99" s="11" t="n">
         <v>7</v>
       </c>
       <c r="C99" s="11" t="n">
-        <v>38079976</v>
+        <v>47129600</v>
       </c>
       <c r="D99" s="12" t="inlineStr">
         <is>
-          <t>1.32%→1.46%</t>
+          <t>2.26%→2.45%</t>
         </is>
       </c>
       <c r="E99" s="13" t="inlineStr">
         <is>
-          <t>58→65</t>
+          <t>77→84</t>
         </is>
       </c>
       <c r="G99" s="17" t="n"/>
@@ -4037,11 +4037,11 @@
         <v>6</v>
       </c>
       <c r="C100" s="11" t="n">
-        <v>36710377</v>
+        <v>34329600</v>
       </c>
       <c r="D100" s="12" t="inlineStr">
         <is>
-          <t>1.84%→1.98%</t>
+          <t>1.80%→1.94%</t>
         </is>
       </c>
       <c r="E100" s="13" t="inlineStr">
@@ -4065,11 +4065,11 @@
         <v>6</v>
       </c>
       <c r="C101" s="11" t="n">
-        <v>21427187</v>
+        <v>21235200</v>
       </c>
       <c r="D101" s="12" t="inlineStr">
         <is>
-          <t>0.12%→0.21%</t>
+          <t>0.12%→0.22%</t>
         </is>
       </c>
       <c r="E101" s="13" t="inlineStr">
@@ -4101,870 +4101,1988 @@
       <c r="K103" s="19" t="n"/>
     </row>
     <row r="105" ht="19" customHeight="1">
-      <c r="A105" s="18" t="inlineStr">
-        <is>
-          <t>■ TIGER 기술이전바이오액티브  (미래에셋)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B105" s="19" t="n"/>
-      <c r="C105" s="19" t="n"/>
-      <c r="D105" s="19" t="n"/>
-      <c r="E105" s="19" t="n"/>
-      <c r="F105" s="19" t="n"/>
-      <c r="G105" s="19" t="n"/>
-      <c r="H105" s="19" t="n"/>
-      <c r="I105" s="19" t="n"/>
-      <c r="J105" s="19" t="n"/>
-      <c r="K105" s="19" t="n"/>
-    </row>
-    <row r="107" ht="19" customHeight="1">
-      <c r="A107" s="3" t="inlineStr">
-        <is>
-          <t>■ DS 코스닥액티브  (DS)      순자산 ≈ 855억   ·   현금 2억(0.2%)      오늘 2026-10-27  vs  5일전 2026-10-20      매수 14종목  /  매도 17종목</t>
-        </is>
-      </c>
-      <c r="B107" s="4" t="n"/>
-      <c r="C107" s="4" t="n"/>
-      <c r="D107" s="4" t="n"/>
-      <c r="E107" s="4" t="n"/>
-      <c r="F107" s="4" t="n"/>
-      <c r="G107" s="4" t="n"/>
-      <c r="H107" s="4" t="n"/>
-      <c r="I107" s="4" t="n"/>
-      <c r="J107" s="4" t="n"/>
-      <c r="K107" s="4" t="n"/>
+      <c r="A105" s="3" t="inlineStr">
+        <is>
+          <t>■ TIGER 기술이전바이오액티브  (미래에셋)      순자산 ≈ 1,035억   ·   현금 69억(6.6%)      오늘 2026-10-27  vs  5일전 2026-10-20      매수 2종목  /  매도 4종목</t>
+        </is>
+      </c>
+      <c r="B105" s="4" t="n"/>
+      <c r="C105" s="4" t="n"/>
+      <c r="D105" s="4" t="n"/>
+      <c r="E105" s="4" t="n"/>
+      <c r="F105" s="4" t="n"/>
+      <c r="G105" s="4" t="n"/>
+      <c r="H105" s="4" t="n"/>
+      <c r="I105" s="4" t="n"/>
+      <c r="J105" s="4" t="n"/>
+      <c r="K105" s="4" t="n"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B106" s="6" t="n"/>
+      <c r="C106" s="6" t="n"/>
+      <c r="D106" s="6" t="n"/>
+      <c r="E106" s="6" t="n"/>
+      <c r="G106" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H106" s="8" t="n"/>
+      <c r="I106" s="8" t="n"/>
+      <c r="J106" s="8" t="n"/>
+      <c r="K106" s="8" t="n"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B107" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C107" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D107" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E107" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G107" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H107" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I107" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J107" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K107" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
     </row>
     <row r="108">
-      <c r="A108" s="5" t="inlineStr">
+      <c r="A108" s="10" t="inlineStr">
+        <is>
+          <t>프로티나</t>
+        </is>
+      </c>
+      <c r="B108" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="C108" s="11" t="n">
+        <v>386221080</v>
+      </c>
+      <c r="D108" s="12" t="inlineStr">
+        <is>
+          <t>2.97%→2.60%</t>
+        </is>
+      </c>
+      <c r="E108" s="13" t="inlineStr">
+        <is>
+          <t>22→26</t>
+        </is>
+      </c>
+      <c r="G108" s="14" t="inlineStr">
+        <is>
+          <t>와이바이오로직스</t>
+        </is>
+      </c>
+      <c r="H108" s="15" t="n">
+        <v>-4</v>
+      </c>
+      <c r="I108" s="15" t="n">
+        <v>-83708861</v>
+      </c>
+      <c r="J108" s="16" t="inlineStr">
+        <is>
+          <t>0.44%→0.24%</t>
+        </is>
+      </c>
+      <c r="K108" s="13" t="inlineStr">
+        <is>
+          <t>15→11</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="10" t="inlineStr">
+        <is>
+          <t>알지노믹스</t>
+        </is>
+      </c>
+      <c r="B109" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="C109" s="11" t="n">
+        <v>141724903</v>
+      </c>
+      <c r="D109" s="12" t="inlineStr">
+        <is>
+          <t>6.81%→5.18%</t>
+        </is>
+      </c>
+      <c r="E109" s="13" t="inlineStr">
+        <is>
+          <t>103→106</t>
+        </is>
+      </c>
+      <c r="G109" s="14" t="inlineStr">
+        <is>
+          <t>리가켐바이오</t>
+        </is>
+      </c>
+      <c r="H109" s="15" t="n">
+        <v>-4</v>
+      </c>
+      <c r="I109" s="15" t="n">
+        <v>-537891589</v>
+      </c>
+      <c r="J109" s="16" t="inlineStr">
+        <is>
+          <t>7.53%→5.01%</t>
+        </is>
+      </c>
+      <c r="K109" s="13" t="inlineStr">
+        <is>
+          <t>40→36</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="17" t="n"/>
+      <c r="B110" s="17" t="n"/>
+      <c r="C110" s="17" t="n"/>
+      <c r="D110" s="17" t="n"/>
+      <c r="E110" s="17" t="n"/>
+      <c r="G110" s="14" t="inlineStr">
+        <is>
+          <t>오름테라퓨틱</t>
+        </is>
+      </c>
+      <c r="H110" s="15" t="n">
+        <v>-3</v>
+      </c>
+      <c r="I110" s="15" t="n">
+        <v>-100139832</v>
+      </c>
+      <c r="J110" s="16" t="inlineStr">
+        <is>
+          <t>0.42%→0.21%</t>
+        </is>
+      </c>
+      <c r="K110" s="13" t="inlineStr">
+        <is>
+          <t>9→6</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="17" t="n"/>
+      <c r="B111" s="17" t="n"/>
+      <c r="C111" s="17" t="n"/>
+      <c r="D111" s="17" t="n"/>
+      <c r="E111" s="17" t="n"/>
+      <c r="G111" s="14" t="inlineStr">
+        <is>
+          <t>유한양행</t>
+        </is>
+      </c>
+      <c r="H111" s="15" t="n">
+        <v>-3</v>
+      </c>
+      <c r="I111" s="15" t="n">
+        <v>-507847568</v>
+      </c>
+      <c r="J111" s="16" t="inlineStr">
+        <is>
+          <t>0.00%→1.58%</t>
+        </is>
+      </c>
+      <c r="K111" s="13" t="inlineStr">
+        <is>
+          <t>12→9</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="19" customHeight="1">
+      <c r="A113" s="3" t="inlineStr">
+        <is>
+          <t>■ DS 코스닥액티브  (DS)      순자산 ≈ 799억      오늘 2026-10-27  vs  5일전 2026-10-20      매수 14종목  /  매도 17종목</t>
+        </is>
+      </c>
+      <c r="B113" s="4" t="n"/>
+      <c r="C113" s="4" t="n"/>
+      <c r="D113" s="4" t="n"/>
+      <c r="E113" s="4" t="n"/>
+      <c r="F113" s="4" t="n"/>
+      <c r="G113" s="4" t="n"/>
+      <c r="H113" s="4" t="n"/>
+      <c r="I113" s="4" t="n"/>
+      <c r="J113" s="4" t="n"/>
+      <c r="K113" s="4" t="n"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="5" t="inlineStr">
         <is>
           <t>🔴 매수 (확대·신규편입)</t>
         </is>
       </c>
-      <c r="B108" s="6" t="n"/>
-      <c r="C108" s="6" t="n"/>
-      <c r="D108" s="6" t="n"/>
-      <c r="E108" s="6" t="n"/>
-      <c r="G108" s="7" t="inlineStr">
+      <c r="B114" s="6" t="n"/>
+      <c r="C114" s="6" t="n"/>
+      <c r="D114" s="6" t="n"/>
+      <c r="E114" s="6" t="n"/>
+      <c r="G114" s="7" t="inlineStr">
         <is>
           <t>🔵 매도 (축소·편출)</t>
         </is>
       </c>
-      <c r="H108" s="8" t="n"/>
-      <c r="I108" s="8" t="n"/>
-      <c r="J108" s="8" t="n"/>
-      <c r="K108" s="8" t="n"/>
-    </row>
-    <row r="109">
-      <c r="A109" s="9" t="inlineStr">
+      <c r="H114" s="8" t="n"/>
+      <c r="I114" s="8" t="n"/>
+      <c r="J114" s="8" t="n"/>
+      <c r="K114" s="8" t="n"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="B109" s="9" t="inlineStr">
+      <c r="B115" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="C109" s="9" t="inlineStr">
+      <c r="C115" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="D109" s="9" t="inlineStr">
+      <c r="D115" s="9" t="inlineStr">
         <is>
           <t>보유비중(전→당)</t>
         </is>
       </c>
-      <c r="E109" s="9" t="inlineStr">
+      <c r="E115" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
         </is>
       </c>
-      <c r="G109" s="9" t="inlineStr">
+      <c r="G115" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="H109" s="9" t="inlineStr">
+      <c r="H115" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="I109" s="9" t="inlineStr">
+      <c r="I115" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="J109" s="9" t="inlineStr">
+      <c r="J115" s="9" t="inlineStr">
         <is>
           <t>보유비중(전→당)</t>
         </is>
       </c>
-      <c r="K109" s="9" t="inlineStr">
+      <c r="K115" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="10" t="inlineStr">
-        <is>
-          <t>뉴파워프라즈마</t>
-        </is>
-      </c>
-      <c r="B110" s="11" t="n">
-        <v>668</v>
-      </c>
-      <c r="C110" s="11" t="n">
-        <v>1492431887</v>
-      </c>
-      <c r="D110" s="12" t="inlineStr">
-        <is>
-          <t>1.83%→3.98%</t>
-        </is>
-      </c>
-      <c r="E110" s="13" t="inlineStr">
-        <is>
-          <t>759→1,427</t>
-        </is>
-      </c>
-      <c r="G110" s="14" t="inlineStr">
-        <is>
-          <t>엠케이전자</t>
-        </is>
-      </c>
-      <c r="H110" s="15" t="n">
-        <v>-597</v>
-      </c>
-      <c r="I110" s="15" t="n">
-        <v>-1327751566</v>
-      </c>
-      <c r="J110" s="16" t="inlineStr">
-        <is>
-          <t>3.59%→1.50%</t>
-        </is>
-      </c>
-      <c r="K110" s="13" t="inlineStr">
-        <is>
-          <t>1,137→540</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="10" t="inlineStr">
-        <is>
-          <t>에프에스티  (신규)</t>
-        </is>
-      </c>
-      <c r="B111" s="11" t="n">
-        <v>408</v>
-      </c>
-      <c r="C111" s="11" t="n">
-        <v>1685876001</v>
-      </c>
-      <c r="D111" s="12" t="inlineStr">
-        <is>
-          <t>0.00%→2.10%</t>
-        </is>
-      </c>
-      <c r="E111" s="13" t="inlineStr">
-        <is>
-          <t>0→408</t>
-        </is>
-      </c>
-      <c r="G111" s="14" t="inlineStr">
-        <is>
-          <t>코세스</t>
-        </is>
-      </c>
-      <c r="H111" s="15" t="n">
-        <v>-385</v>
-      </c>
-      <c r="I111" s="15" t="n">
-        <v>-2127624996</v>
-      </c>
-      <c r="J111" s="16" t="inlineStr">
-        <is>
-          <t>3.79%→1.70%</t>
-        </is>
-      </c>
-      <c r="K111" s="13" t="inlineStr">
-        <is>
-          <t>631→246</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="10" t="inlineStr">
-        <is>
-          <t>아스플로</t>
-        </is>
-      </c>
-      <c r="B112" s="11" t="n">
-        <v>283</v>
-      </c>
-      <c r="C112" s="11" t="n">
-        <v>1384591322</v>
-      </c>
-      <c r="D112" s="12" t="inlineStr">
-        <is>
-          <t>1.92%→3.82%</t>
-        </is>
-      </c>
-      <c r="E112" s="13" t="inlineStr">
-        <is>
-          <t>343→626</t>
-        </is>
-      </c>
-      <c r="G112" s="14" t="inlineStr">
-        <is>
-          <t>SFA  (편출)</t>
-        </is>
-      </c>
-      <c r="H112" s="15" t="n">
-        <v>-320</v>
-      </c>
-      <c r="I112" s="15" t="n">
-        <v>-1519647640</v>
-      </c>
-      <c r="J112" s="16" t="inlineStr">
-        <is>
-          <t>1.71%→0.00%</t>
-        </is>
-      </c>
-      <c r="K112" s="13" t="inlineStr">
-        <is>
-          <t>320→0</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="10" t="inlineStr">
-        <is>
-          <t>샘씨엔에스</t>
-        </is>
-      </c>
-      <c r="B113" s="11" t="n">
-        <v>243</v>
-      </c>
-      <c r="C113" s="11" t="n">
-        <v>629146291</v>
-      </c>
-      <c r="D113" s="12" t="inlineStr">
-        <is>
-          <t>4.95%→6.08%</t>
-        </is>
-      </c>
-      <c r="E113" s="13" t="inlineStr">
-        <is>
-          <t>1,640→1,883</t>
-        </is>
-      </c>
-      <c r="G113" s="14" t="inlineStr">
-        <is>
-          <t>저스템</t>
-        </is>
-      </c>
-      <c r="H113" s="15" t="n">
-        <v>-237</v>
-      </c>
-      <c r="I113" s="15" t="n">
-        <v>-509474039</v>
-      </c>
-      <c r="J113" s="16" t="inlineStr">
-        <is>
-          <t>2.64%→1.89%</t>
-        </is>
-      </c>
-      <c r="K113" s="13" t="inlineStr">
-        <is>
-          <t>942→705</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="10" t="inlineStr">
-        <is>
-          <t>RFHIC  (신규)</t>
-        </is>
-      </c>
-      <c r="B114" s="11" t="n">
-        <v>209</v>
-      </c>
-      <c r="C114" s="11" t="n">
-        <v>1665384756</v>
-      </c>
-      <c r="D114" s="12" t="inlineStr">
-        <is>
-          <t>0.00%→2.08%</t>
-        </is>
-      </c>
-      <c r="E114" s="13" t="inlineStr">
-        <is>
-          <t>0→209</t>
-        </is>
-      </c>
-      <c r="G114" s="14" t="inlineStr">
-        <is>
-          <t>디케이티</t>
-        </is>
-      </c>
-      <c r="H114" s="15" t="n">
-        <v>-189</v>
-      </c>
-      <c r="I114" s="15" t="n">
-        <v>-785748414</v>
-      </c>
-      <c r="J114" s="16" t="inlineStr">
-        <is>
-          <t>4.73%→5.01%</t>
-        </is>
-      </c>
-      <c r="K114" s="13" t="inlineStr">
-        <is>
-          <t>1,155→966</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="10" t="inlineStr">
-        <is>
-          <t>에스티아이</t>
-        </is>
-      </c>
-      <c r="B115" s="11" t="n">
-        <v>168</v>
-      </c>
-      <c r="C115" s="11" t="n">
-        <v>670051041</v>
-      </c>
-      <c r="D115" s="12" t="inlineStr">
-        <is>
-          <t>2.09%→2.65%</t>
-        </is>
-      </c>
-      <c r="E115" s="13" t="inlineStr">
-        <is>
-          <t>365→533</t>
-        </is>
-      </c>
-      <c r="G115" s="14" t="inlineStr">
-        <is>
-          <t>태웅  (편출)</t>
-        </is>
-      </c>
-      <c r="H115" s="15" t="n">
-        <v>-186</v>
-      </c>
-      <c r="I115" s="15" t="n">
-        <v>-936732978</v>
-      </c>
-      <c r="J115" s="16" t="inlineStr">
-        <is>
-          <t>1.06%→0.00%</t>
-        </is>
-      </c>
-      <c r="K115" s="13" t="inlineStr">
-        <is>
-          <t>186→0</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="10" t="inlineStr">
         <is>
-          <t>동진쎄미켐</t>
+          <t>뉴파워프라즈마</t>
         </is>
       </c>
       <c r="B116" s="11" t="n">
-        <v>95</v>
+        <v>668</v>
       </c>
       <c r="C116" s="11" t="n">
-        <v>598048608</v>
+        <v>1483601986</v>
       </c>
       <c r="D116" s="12" t="inlineStr">
         <is>
-          <t>2.21%→2.91%</t>
+          <t>1.83%→3.98%</t>
         </is>
       </c>
       <c r="E116" s="13" t="inlineStr">
         <is>
-          <t>275→370</t>
+          <t>759→1,427</t>
         </is>
       </c>
       <c r="G116" s="14" t="inlineStr">
         <is>
-          <t>네오셈</t>
+          <t>엠케이전자</t>
         </is>
       </c>
       <c r="H116" s="15" t="n">
-        <v>-108</v>
+        <v>-597</v>
       </c>
       <c r="I116" s="15" t="n">
-        <v>-275970175</v>
+        <v>-1319895989</v>
       </c>
       <c r="J116" s="16" t="inlineStr">
         <is>
-          <t>2.34%→2.20%</t>
+          <t>3.59%→1.50%</t>
         </is>
       </c>
       <c r="K116" s="13" t="inlineStr">
         <is>
-          <t>797→689</t>
+          <t>1,137→540</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="10" t="inlineStr">
         <is>
-          <t>코미코</t>
+          <t>에프에스티  (신규)</t>
         </is>
       </c>
       <c r="B117" s="11" t="n">
-        <v>86</v>
+        <v>408</v>
       </c>
       <c r="C117" s="11" t="n">
-        <v>332101821</v>
+        <v>1675901598</v>
       </c>
       <c r="D117" s="12" t="inlineStr">
         <is>
-          <t>1.49%→1.92%</t>
+          <t>0.00%→2.10%</t>
         </is>
       </c>
       <c r="E117" s="13" t="inlineStr">
         <is>
-          <t>313→399</t>
+          <t>0→408</t>
         </is>
       </c>
       <c r="G117" s="14" t="inlineStr">
         <is>
-          <t>싸이맥스  (편출)</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="H117" s="15" t="n">
-        <v>-85</v>
+        <v>-385</v>
       </c>
       <c r="I117" s="15" t="n">
-        <v>-313156926</v>
+        <v>-2115037007</v>
       </c>
       <c r="J117" s="16" t="inlineStr">
         <is>
-          <t>0.35%→0.00%</t>
+          <t>3.79%→1.70%</t>
         </is>
       </c>
       <c r="K117" s="13" t="inlineStr">
         <is>
-          <t>85→0</t>
+          <t>631→246</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="10" t="inlineStr">
         <is>
-          <t>미코</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="B118" s="11" t="n">
-        <v>78</v>
+        <v>283</v>
       </c>
       <c r="C118" s="11" t="n">
-        <v>266276337</v>
+        <v>1376399455</v>
       </c>
       <c r="D118" s="12" t="inlineStr">
         <is>
-          <t>4.80%→5.47%</t>
+          <t>1.92%→3.82%</t>
         </is>
       </c>
       <c r="E118" s="13" t="inlineStr">
         <is>
-          <t>1,206→1,284</t>
+          <t>343→626</t>
         </is>
       </c>
       <c r="G118" s="14" t="inlineStr">
         <is>
-          <t>리노공업</t>
+          <t>SFA  (편출)</t>
         </is>
       </c>
       <c r="H118" s="15" t="n">
-        <v>-61</v>
+        <v>-320</v>
       </c>
       <c r="I118" s="15" t="n">
-        <v>-608230856</v>
+        <v>-1510656719</v>
       </c>
       <c r="J118" s="16" t="inlineStr">
         <is>
-          <t>4.68%→3.65%</t>
+          <t>1.71%→0.00%</t>
         </is>
       </c>
       <c r="K118" s="13" t="inlineStr">
         <is>
-          <t>354→293</t>
+          <t>320→0</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="10" t="inlineStr">
         <is>
-          <t>인텍플러스</t>
+          <t>샘씨엔에스</t>
         </is>
       </c>
       <c r="B119" s="11" t="n">
-        <v>51</v>
+        <v>243</v>
       </c>
       <c r="C119" s="11" t="n">
-        <v>447325994</v>
+        <v>625423978</v>
       </c>
       <c r="D119" s="12" t="inlineStr">
         <is>
-          <t>2.44%→2.92%</t>
+          <t>4.95%→6.08%</t>
         </is>
       </c>
       <c r="E119" s="13" t="inlineStr">
         <is>
-          <t>216→267</t>
+          <t>1,640→1,883</t>
         </is>
       </c>
       <c r="G119" s="14" t="inlineStr">
         <is>
-          <t>원익QnC  (편출)</t>
+          <t>저스템</t>
         </is>
       </c>
       <c r="H119" s="15" t="n">
-        <v>-57</v>
+        <v>-237</v>
       </c>
       <c r="I119" s="15" t="n">
-        <v>-265870737</v>
+        <v>-506459761</v>
       </c>
       <c r="J119" s="16" t="inlineStr">
         <is>
-          <t>0.30%→0.00%</t>
+          <t>2.64%→1.89%</t>
         </is>
       </c>
       <c r="K119" s="13" t="inlineStr">
         <is>
-          <t>57→0</t>
+          <t>942→705</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="10" t="inlineStr">
         <is>
-          <t>기가비스</t>
+          <t>RFHIC  (신규)</t>
         </is>
       </c>
       <c r="B120" s="11" t="n">
-        <v>46</v>
+        <v>209</v>
       </c>
       <c r="C120" s="11" t="n">
-        <v>753300422</v>
+        <v>1655531588</v>
       </c>
       <c r="D120" s="12" t="inlineStr">
         <is>
-          <t>1.07%→1.96%</t>
+          <t>0.00%→2.08%</t>
         </is>
       </c>
       <c r="E120" s="13" t="inlineStr">
         <is>
-          <t>50→96</t>
+          <t>0→209</t>
         </is>
       </c>
       <c r="G120" s="14" t="inlineStr">
         <is>
-          <t>제주반도체</t>
+          <t>디케이티</t>
         </is>
       </c>
       <c r="H120" s="15" t="n">
-        <v>-49</v>
+        <v>-189</v>
       </c>
       <c r="I120" s="15" t="n">
-        <v>-507625180</v>
+        <v>-781099572</v>
       </c>
       <c r="J120" s="16" t="inlineStr">
         <is>
-          <t>1.15%→0.49%</t>
+          <t>4.73%→5.01%</t>
         </is>
       </c>
       <c r="K120" s="13" t="inlineStr">
         <is>
-          <t>87→38</t>
+          <t>1,155→966</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="10" t="inlineStr">
         <is>
-          <t>이엔에프테크놀로지</t>
+          <t>에스티아이</t>
         </is>
       </c>
       <c r="B121" s="11" t="n">
-        <v>32</v>
+        <v>168</v>
       </c>
       <c r="C121" s="11" t="n">
-        <v>211452750</v>
+        <v>666086717</v>
       </c>
       <c r="D121" s="12" t="inlineStr">
         <is>
-          <t>3.14%→3.36%</t>
+          <t>2.09%→2.65%</t>
         </is>
       </c>
       <c r="E121" s="13" t="inlineStr">
         <is>
-          <t>376→408</t>
+          <t>365→533</t>
         </is>
       </c>
       <c r="G121" s="14" t="inlineStr">
         <is>
-          <t>프로텍</t>
+          <t>태웅  (편출)</t>
         </is>
       </c>
       <c r="H121" s="15" t="n">
-        <v>-41</v>
+        <v>-186</v>
       </c>
       <c r="I121" s="15" t="n">
-        <v>-396338706</v>
+        <v>-931190843</v>
       </c>
       <c r="J121" s="16" t="inlineStr">
         <is>
-          <t>0.94%→0.40%</t>
+          <t>1.06%→0.00%</t>
         </is>
       </c>
       <c r="K121" s="13" t="inlineStr">
         <is>
-          <t>74→33</t>
+          <t>186→0</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="10" t="inlineStr">
         <is>
-          <t>파두</t>
+          <t>동진쎄미켐</t>
         </is>
       </c>
       <c r="B122" s="11" t="n">
-        <v>30</v>
+        <v>95</v>
       </c>
       <c r="C122" s="11" t="n">
-        <v>227135946</v>
+        <v>594510283</v>
       </c>
       <c r="D122" s="12" t="inlineStr">
         <is>
-          <t>1.73%→1.85%</t>
+          <t>2.21%→2.91%</t>
         </is>
       </c>
       <c r="E122" s="13" t="inlineStr">
         <is>
-          <t>166→196</t>
+          <t>275→370</t>
         </is>
       </c>
       <c r="G122" s="14" t="inlineStr">
         <is>
-          <t>티씨케이  (편출)</t>
+          <t>네오셈</t>
         </is>
       </c>
       <c r="H122" s="15" t="n">
-        <v>-13</v>
+        <v>-108</v>
       </c>
       <c r="I122" s="15" t="n">
-        <v>-515196378</v>
+        <v>-274337411</v>
       </c>
       <c r="J122" s="16" t="inlineStr">
         <is>
-          <t>0.58%→0.00%</t>
+          <t>2.34%→2.20%</t>
         </is>
       </c>
       <c r="K122" s="13" t="inlineStr">
         <is>
-          <t>13→0</t>
+          <t>797→689</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="10" t="inlineStr">
         <is>
+          <t>코미코</t>
+        </is>
+      </c>
+      <c r="B123" s="11" t="n">
+        <v>86</v>
+      </c>
+      <c r="C123" s="11" t="n">
+        <v>330136957</v>
+      </c>
+      <c r="D123" s="12" t="inlineStr">
+        <is>
+          <t>1.49%→1.92%</t>
+        </is>
+      </c>
+      <c r="E123" s="13" t="inlineStr">
+        <is>
+          <t>313→399</t>
+        </is>
+      </c>
+      <c r="G123" s="14" t="inlineStr">
+        <is>
+          <t>싸이맥스  (편출)</t>
+        </is>
+      </c>
+      <c r="H123" s="15" t="n">
+        <v>-85</v>
+      </c>
+      <c r="I123" s="15" t="n">
+        <v>-311304148</v>
+      </c>
+      <c r="J123" s="16" t="inlineStr">
+        <is>
+          <t>0.35%→0.00%</t>
+        </is>
+      </c>
+      <c r="K123" s="13" t="inlineStr">
+        <is>
+          <t>85→0</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="10" t="inlineStr">
+        <is>
+          <t>미코</t>
+        </is>
+      </c>
+      <c r="B124" s="11" t="n">
+        <v>78</v>
+      </c>
+      <c r="C124" s="11" t="n">
+        <v>264700926</v>
+      </c>
+      <c r="D124" s="12" t="inlineStr">
+        <is>
+          <t>4.80%→5.47%</t>
+        </is>
+      </c>
+      <c r="E124" s="13" t="inlineStr">
+        <is>
+          <t>1,206→1,284</t>
+        </is>
+      </c>
+      <c r="G124" s="14" t="inlineStr">
+        <is>
+          <t>리노공업</t>
+        </is>
+      </c>
+      <c r="H124" s="15" t="n">
+        <v>-61</v>
+      </c>
+      <c r="I124" s="15" t="n">
+        <v>-604632288</v>
+      </c>
+      <c r="J124" s="16" t="inlineStr">
+        <is>
+          <t>4.68%→3.65%</t>
+        </is>
+      </c>
+      <c r="K124" s="13" t="inlineStr">
+        <is>
+          <t>354→293</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="10" t="inlineStr">
+        <is>
+          <t>인텍플러스</t>
+        </is>
+      </c>
+      <c r="B125" s="11" t="n">
+        <v>51</v>
+      </c>
+      <c r="C125" s="11" t="n">
+        <v>444679412</v>
+      </c>
+      <c r="D125" s="12" t="inlineStr">
+        <is>
+          <t>2.44%→2.92%</t>
+        </is>
+      </c>
+      <c r="E125" s="13" t="inlineStr">
+        <is>
+          <t>216→267</t>
+        </is>
+      </c>
+      <c r="G125" s="14" t="inlineStr">
+        <is>
+          <t>원익QnC  (편출)</t>
+        </is>
+      </c>
+      <c r="H125" s="15" t="n">
+        <v>-57</v>
+      </c>
+      <c r="I125" s="15" t="n">
+        <v>-264297726</v>
+      </c>
+      <c r="J125" s="16" t="inlineStr">
+        <is>
+          <t>0.30%→0.00%</t>
+        </is>
+      </c>
+      <c r="K125" s="13" t="inlineStr">
+        <is>
+          <t>57→0</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="10" t="inlineStr">
+        <is>
+          <t>기가비스</t>
+        </is>
+      </c>
+      <c r="B126" s="11" t="n">
+        <v>46</v>
+      </c>
+      <c r="C126" s="11" t="n">
+        <v>748843557</v>
+      </c>
+      <c r="D126" s="12" t="inlineStr">
+        <is>
+          <t>1.07%→1.96%</t>
+        </is>
+      </c>
+      <c r="E126" s="13" t="inlineStr">
+        <is>
+          <t>50→96</t>
+        </is>
+      </c>
+      <c r="G126" s="14" t="inlineStr">
+        <is>
+          <t>제주반도체</t>
+        </is>
+      </c>
+      <c r="H126" s="15" t="n">
+        <v>-49</v>
+      </c>
+      <c r="I126" s="15" t="n">
+        <v>-504621840</v>
+      </c>
+      <c r="J126" s="16" t="inlineStr">
+        <is>
+          <t>1.15%→0.49%</t>
+        </is>
+      </c>
+      <c r="K126" s="13" t="inlineStr">
+        <is>
+          <t>87→38</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="10" t="inlineStr">
+        <is>
+          <t>이엔에프테크놀로지</t>
+        </is>
+      </c>
+      <c r="B127" s="11" t="n">
+        <v>32</v>
+      </c>
+      <c r="C127" s="11" t="n">
+        <v>210201700</v>
+      </c>
+      <c r="D127" s="12" t="inlineStr">
+        <is>
+          <t>3.14%→3.36%</t>
+        </is>
+      </c>
+      <c r="E127" s="13" t="inlineStr">
+        <is>
+          <t>376→408</t>
+        </is>
+      </c>
+      <c r="G127" s="14" t="inlineStr">
+        <is>
+          <t>프로텍</t>
+        </is>
+      </c>
+      <c r="H127" s="15" t="n">
+        <v>-41</v>
+      </c>
+      <c r="I127" s="15" t="n">
+        <v>-393993788</v>
+      </c>
+      <c r="J127" s="16" t="inlineStr">
+        <is>
+          <t>0.94%→0.40%</t>
+        </is>
+      </c>
+      <c r="K127" s="13" t="inlineStr">
+        <is>
+          <t>74→33</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="10" t="inlineStr">
+        <is>
+          <t>파두</t>
+        </is>
+      </c>
+      <c r="B128" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="C128" s="11" t="n">
+        <v>225792108</v>
+      </c>
+      <c r="D128" s="12" t="inlineStr">
+        <is>
+          <t>1.73%→1.85%</t>
+        </is>
+      </c>
+      <c r="E128" s="13" t="inlineStr">
+        <is>
+          <t>166→196</t>
+        </is>
+      </c>
+      <c r="G128" s="14" t="inlineStr">
+        <is>
+          <t>티씨케이  (편출)</t>
+        </is>
+      </c>
+      <c r="H128" s="15" t="n">
+        <v>-13</v>
+      </c>
+      <c r="I128" s="15" t="n">
+        <v>-512148244</v>
+      </c>
+      <c r="J128" s="16" t="inlineStr">
+        <is>
+          <t>0.58%→0.00%</t>
+        </is>
+      </c>
+      <c r="K128" s="13" t="inlineStr">
+        <is>
+          <t>13→0</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="10" t="inlineStr">
+        <is>
           <t>솔브레인</t>
         </is>
       </c>
-      <c r="B123" s="11" t="n">
+      <c r="B129" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="C123" s="11" t="n">
-        <v>292538931</v>
-      </c>
-      <c r="D123" s="12" t="inlineStr">
+      <c r="C129" s="11" t="n">
+        <v>290808138</v>
+      </c>
+      <c r="D129" s="12" t="inlineStr">
         <is>
           <t>2.89%→3.10%</t>
         </is>
       </c>
-      <c r="E123" s="13" t="inlineStr">
+      <c r="E129" s="13" t="inlineStr">
         <is>
           <t>45→51</t>
         </is>
       </c>
-      <c r="G123" s="14" t="inlineStr">
+      <c r="G129" s="14" t="inlineStr">
         <is>
           <t>파크시스템스</t>
         </is>
       </c>
-      <c r="H123" s="15" t="n">
+      <c r="H129" s="15" t="n">
         <v>-7</v>
       </c>
-      <c r="I123" s="15" t="n">
-        <v>-263808938</v>
-      </c>
-      <c r="J123" s="16" t="inlineStr">
+      <c r="I129" s="15" t="n">
+        <v>-262248125</v>
+      </c>
+      <c r="J129" s="16" t="inlineStr">
         <is>
           <t>1.94%→1.55%</t>
         </is>
       </c>
-      <c r="K123" s="13" t="inlineStr">
+      <c r="K129" s="13" t="inlineStr">
         <is>
           <t>40→33</t>
         </is>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="17" t="n"/>
-      <c r="B124" s="17" t="n"/>
-      <c r="C124" s="17" t="n"/>
-      <c r="D124" s="17" t="n"/>
-      <c r="E124" s="17" t="n"/>
-      <c r="G124" s="14" t="inlineStr">
+    <row r="130">
+      <c r="A130" s="17" t="n"/>
+      <c r="B130" s="17" t="n"/>
+      <c r="C130" s="17" t="n"/>
+      <c r="D130" s="17" t="n"/>
+      <c r="E130" s="17" t="n"/>
+      <c r="G130" s="14" t="inlineStr">
         <is>
           <t>피에스케이홀딩스</t>
         </is>
       </c>
-      <c r="H124" s="15" t="n">
+      <c r="H130" s="15" t="n">
         <v>-5</v>
       </c>
-      <c r="I124" s="15" t="n">
-        <v>-133256468</v>
-      </c>
-      <c r="J124" s="16" t="inlineStr">
+      <c r="I130" s="15" t="n">
+        <v>-132468063</v>
+      </c>
+      <c r="J130" s="16" t="inlineStr">
         <is>
           <t>2.54%→2.13%</t>
         </is>
       </c>
-      <c r="K124" s="13" t="inlineStr">
+      <c r="K130" s="13" t="inlineStr">
         <is>
           <t>69→64</t>
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="17" t="n"/>
-      <c r="B125" s="17" t="n"/>
-      <c r="C125" s="17" t="n"/>
-      <c r="D125" s="17" t="n"/>
-      <c r="E125" s="17" t="n"/>
-      <c r="G125" s="14" t="inlineStr">
+    <row r="131">
+      <c r="A131" s="17" t="n"/>
+      <c r="B131" s="17" t="n"/>
+      <c r="C131" s="17" t="n"/>
+      <c r="D131" s="17" t="n"/>
+      <c r="E131" s="17" t="n"/>
+      <c r="G131" s="14" t="inlineStr">
+        <is>
+          <t>티에스이</t>
+        </is>
+      </c>
+      <c r="H131" s="15" t="n">
+        <v>-4</v>
+      </c>
+      <c r="I131" s="15" t="n">
+        <v>-161952077</v>
+      </c>
+      <c r="J131" s="16" t="inlineStr">
+        <is>
+          <t>2.45%→2.13%</t>
+        </is>
+      </c>
+      <c r="K131" s="13" t="inlineStr">
+        <is>
+          <t>46→42</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="17" t="n"/>
+      <c r="B132" s="17" t="n"/>
+      <c r="C132" s="17" t="n"/>
+      <c r="D132" s="17" t="n"/>
+      <c r="E132" s="17" t="n"/>
+      <c r="G132" s="14" t="inlineStr">
         <is>
           <t>이오테크닉스</t>
         </is>
       </c>
-      <c r="H125" s="15" t="n">
+      <c r="H132" s="15" t="n">
         <v>-4</v>
       </c>
-      <c r="I125" s="15" t="n">
-        <v>-256203939</v>
-      </c>
-      <c r="J125" s="16" t="inlineStr">
+      <c r="I132" s="15" t="n">
+        <v>-254688121</v>
+      </c>
+      <c r="J132" s="16" t="inlineStr">
         <is>
           <t>4.42%→3.92%</t>
         </is>
       </c>
-      <c r="K125" s="13" t="inlineStr">
+      <c r="K132" s="13" t="inlineStr">
         <is>
           <t>53→49</t>
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="17" t="n"/>
-      <c r="B126" s="17" t="n"/>
-      <c r="C126" s="17" t="n"/>
-      <c r="D126" s="17" t="n"/>
-      <c r="E126" s="17" t="n"/>
-      <c r="G126" s="14" t="inlineStr">
-        <is>
-          <t>티에스이</t>
-        </is>
-      </c>
-      <c r="H126" s="15" t="n">
+    <row r="134" ht="19" customHeight="1">
+      <c r="A134" s="3" t="inlineStr">
+        <is>
+          <t>■ TIGER 코스닥액티브  (미래에셋)      순자산 ≈ 281억   ·   현금 2억(0.7%)      오늘 2026-10-27  vs  5일전 2026-10-20      매수 9종목  /  매도 16종목</t>
+        </is>
+      </c>
+      <c r="B134" s="4" t="n"/>
+      <c r="C134" s="4" t="n"/>
+      <c r="D134" s="4" t="n"/>
+      <c r="E134" s="4" t="n"/>
+      <c r="F134" s="4" t="n"/>
+      <c r="G134" s="4" t="n"/>
+      <c r="H134" s="4" t="n"/>
+      <c r="I134" s="4" t="n"/>
+      <c r="J134" s="4" t="n"/>
+      <c r="K134" s="4" t="n"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B135" s="6" t="n"/>
+      <c r="C135" s="6" t="n"/>
+      <c r="D135" s="6" t="n"/>
+      <c r="E135" s="6" t="n"/>
+      <c r="G135" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H135" s="8" t="n"/>
+      <c r="I135" s="8" t="n"/>
+      <c r="J135" s="8" t="n"/>
+      <c r="K135" s="8" t="n"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B136" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C136" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D136" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E136" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G136" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H136" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I136" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J136" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K136" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="10" t="inlineStr">
+        <is>
+          <t>파인엠텍  (신규)</t>
+        </is>
+      </c>
+      <c r="B137" s="11" t="n">
+        <v>77</v>
+      </c>
+      <c r="C137" s="11" t="n">
+        <v>307615217</v>
+      </c>
+      <c r="D137" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→1.10%</t>
+        </is>
+      </c>
+      <c r="E137" s="13" t="inlineStr">
+        <is>
+          <t>0→77</t>
+        </is>
+      </c>
+      <c r="G137" s="14" t="inlineStr">
+        <is>
+          <t>동국산업</t>
+        </is>
+      </c>
+      <c r="H137" s="15" t="n">
+        <v>-136</v>
+      </c>
+      <c r="I137" s="15" t="n">
+        <v>-208658147</v>
+      </c>
+      <c r="J137" s="16" t="inlineStr">
+        <is>
+          <t>1.73%→0.93%</t>
+        </is>
+      </c>
+      <c r="K137" s="13" t="inlineStr">
+        <is>
+          <t>306→170</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="10" t="inlineStr">
+        <is>
+          <t>루닛  (신규)</t>
+        </is>
+      </c>
+      <c r="B138" s="11" t="n">
+        <v>61</v>
+      </c>
+      <c r="C138" s="11" t="n">
+        <v>380838519</v>
+      </c>
+      <c r="D138" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→1.36%</t>
+        </is>
+      </c>
+      <c r="E138" s="13" t="inlineStr">
+        <is>
+          <t>0→61</t>
+        </is>
+      </c>
+      <c r="G138" s="14" t="inlineStr">
+        <is>
+          <t>피엠티</t>
+        </is>
+      </c>
+      <c r="H138" s="15" t="n">
+        <v>-50</v>
+      </c>
+      <c r="I138" s="15" t="n">
+        <v>-67468798</v>
+      </c>
+      <c r="J138" s="16" t="inlineStr">
+        <is>
+          <t>0.26%→0.01%</t>
+        </is>
+      </c>
+      <c r="K138" s="13" t="inlineStr">
+        <is>
+          <t>53→3</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="10" t="inlineStr">
+        <is>
+          <t>프로티나  (신규)</t>
+        </is>
+      </c>
+      <c r="B139" s="11" t="n">
+        <v>29</v>
+      </c>
+      <c r="C139" s="11" t="n">
+        <v>574345405</v>
+      </c>
+      <c r="D139" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→2.06%</t>
+        </is>
+      </c>
+      <c r="E139" s="13" t="inlineStr">
+        <is>
+          <t>0→29</t>
+        </is>
+      </c>
+      <c r="G139" s="14" t="inlineStr">
+        <is>
+          <t>덕산하이메탈</t>
+        </is>
+      </c>
+      <c r="H139" s="15" t="n">
+        <v>-50</v>
+      </c>
+      <c r="I139" s="15" t="n">
+        <v>-216325153</v>
+      </c>
+      <c r="J139" s="16" t="inlineStr">
+        <is>
+          <t>1.43%→0.62%</t>
+        </is>
+      </c>
+      <c r="K139" s="13" t="inlineStr">
+        <is>
+          <t>90→40</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="10" t="inlineStr">
+        <is>
+          <t>지투지바이오</t>
+        </is>
+      </c>
+      <c r="B140" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="C140" s="11" t="n">
+        <v>384200271</v>
+      </c>
+      <c r="D140" s="12" t="inlineStr">
+        <is>
+          <t>0.64%→1.99%</t>
+        </is>
+      </c>
+      <c r="E140" s="13" t="inlineStr">
+        <is>
+          <t>9→29</t>
+        </is>
+      </c>
+      <c r="G140" s="14" t="inlineStr">
+        <is>
+          <t>HT로보틱스</t>
+        </is>
+      </c>
+      <c r="H140" s="15" t="n">
+        <v>-46</v>
+      </c>
+      <c r="I140" s="15" t="n">
+        <v>-182988129</v>
+      </c>
+      <c r="J140" s="16" t="inlineStr">
+        <is>
+          <t>0.72%→0.04%</t>
+        </is>
+      </c>
+      <c r="K140" s="13" t="inlineStr">
+        <is>
+          <t>49→3</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="10" t="inlineStr">
+        <is>
+          <t>코세스</t>
+        </is>
+      </c>
+      <c r="B141" s="11" t="n">
+        <v>11</v>
+      </c>
+      <c r="C141" s="11" t="n">
+        <v>152872608</v>
+      </c>
+      <c r="D141" s="12" t="inlineStr">
+        <is>
+          <t>6.24%→6.62%</t>
+        </is>
+      </c>
+      <c r="E141" s="13" t="inlineStr">
+        <is>
+          <t>122→133</t>
+        </is>
+      </c>
+      <c r="G141" s="14" t="inlineStr">
+        <is>
+          <t>피노</t>
+        </is>
+      </c>
+      <c r="H141" s="15" t="n">
+        <v>-40</v>
+      </c>
+      <c r="I141" s="15" t="n">
+        <v>-122060086</v>
+      </c>
+      <c r="J141" s="16" t="inlineStr">
+        <is>
+          <t>3.51%→2.97%</t>
+        </is>
+      </c>
+      <c r="K141" s="13" t="inlineStr">
+        <is>
+          <t>312→272</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="10" t="inlineStr">
+        <is>
+          <t>선익시스템  (신규)</t>
+        </is>
+      </c>
+      <c r="B142" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="C142" s="11" t="n">
+        <v>315945223</v>
+      </c>
+      <c r="D142" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→1.13%</t>
+        </is>
+      </c>
+      <c r="E142" s="13" t="inlineStr">
+        <is>
+          <t>0→9</t>
+        </is>
+      </c>
+      <c r="G142" s="14" t="inlineStr">
+        <is>
+          <t>에이팩트</t>
+        </is>
+      </c>
+      <c r="H142" s="15" t="n">
+        <v>-24</v>
+      </c>
+      <c r="I142" s="15" t="n">
+        <v>-95574067</v>
+      </c>
+      <c r="J142" s="16" t="inlineStr">
+        <is>
+          <t>3.52%→3.08%</t>
+        </is>
+      </c>
+      <c r="K142" s="13" t="inlineStr">
+        <is>
+          <t>240→216</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="10" t="inlineStr">
+        <is>
+          <t>알지노믹스</t>
+        </is>
+      </c>
+      <c r="B143" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="C143" s="11" t="n">
+        <v>87210062</v>
+      </c>
+      <c r="D143" s="12" t="inlineStr">
+        <is>
+          <t>0.75%→1.04%</t>
+        </is>
+      </c>
+      <c r="E143" s="13" t="inlineStr">
+        <is>
+          <t>21→30</t>
+        </is>
+      </c>
+      <c r="G143" s="14" t="inlineStr">
+        <is>
+          <t>한선엔지니어링</t>
+        </is>
+      </c>
+      <c r="H143" s="15" t="n">
+        <v>-18</v>
+      </c>
+      <c r="I143" s="15" t="n">
+        <v>-97843569</v>
+      </c>
+      <c r="J143" s="16" t="inlineStr">
+        <is>
+          <t>2.34%→1.93%</t>
+        </is>
+      </c>
+      <c r="K143" s="13" t="inlineStr">
+        <is>
+          <t>117→99</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="10" t="inlineStr">
+        <is>
+          <t>올릭스</t>
+        </is>
+      </c>
+      <c r="B144" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="C144" s="11" t="n">
+        <v>285897702</v>
+      </c>
+      <c r="D144" s="12" t="inlineStr">
+        <is>
+          <t>2.71%→3.65%</t>
+        </is>
+      </c>
+      <c r="E144" s="13" t="inlineStr">
+        <is>
+          <t>18→25</t>
+        </is>
+      </c>
+      <c r="G144" s="14" t="inlineStr">
+        <is>
+          <t>오킨스전자</t>
+        </is>
+      </c>
+      <c r="H144" s="15" t="n">
+        <v>-12</v>
+      </c>
+      <c r="I144" s="15" t="n">
+        <v>-117810083</v>
+      </c>
+      <c r="J144" s="16" t="inlineStr">
+        <is>
+          <t>1.27%→0.81%</t>
+        </is>
+      </c>
+      <c r="K144" s="13" t="inlineStr">
+        <is>
+          <t>35→23</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="10" t="inlineStr">
+        <is>
+          <t>심텍</t>
+        </is>
+      </c>
+      <c r="B145" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="C145" s="11" t="n">
+        <v>136807597</v>
+      </c>
+      <c r="D145" s="12" t="inlineStr">
+        <is>
+          <t>5.20%→5.55%</t>
+        </is>
+      </c>
+      <c r="E145" s="13" t="inlineStr">
+        <is>
+          <t>31→34</t>
+        </is>
+      </c>
+      <c r="G145" s="14" t="inlineStr">
+        <is>
+          <t>HLB이노베이션</t>
+        </is>
+      </c>
+      <c r="H145" s="15" t="n">
+        <v>-11</v>
+      </c>
+      <c r="I145" s="15" t="n">
+        <v>-69470549</v>
+      </c>
+      <c r="J145" s="16" t="inlineStr">
+        <is>
+          <t>0.93%→0.66%</t>
+        </is>
+      </c>
+      <c r="K145" s="13" t="inlineStr">
+        <is>
+          <t>40→29</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="17" t="n"/>
+      <c r="B146" s="17" t="n"/>
+      <c r="C146" s="17" t="n"/>
+      <c r="D146" s="17" t="n"/>
+      <c r="E146" s="17" t="n"/>
+      <c r="G146" s="14" t="inlineStr">
+        <is>
+          <t>덕산테코피아</t>
+        </is>
+      </c>
+      <c r="H146" s="15" t="n">
+        <v>-9</v>
+      </c>
+      <c r="I146" s="15" t="n">
+        <v>-36643526</v>
+      </c>
+      <c r="J146" s="16" t="inlineStr">
+        <is>
+          <t>0.34%→0.20%</t>
+        </is>
+      </c>
+      <c r="K146" s="13" t="inlineStr">
+        <is>
+          <t>23→14</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="17" t="n"/>
+      <c r="B147" s="17" t="n"/>
+      <c r="C147" s="17" t="n"/>
+      <c r="D147" s="17" t="n"/>
+      <c r="E147" s="17" t="n"/>
+      <c r="G147" s="14" t="inlineStr">
+        <is>
+          <t>오이솔루션</t>
+        </is>
+      </c>
+      <c r="H147" s="15" t="n">
+        <v>-7</v>
+      </c>
+      <c r="I147" s="15" t="n">
+        <v>-71400050</v>
+      </c>
+      <c r="J147" s="16" t="inlineStr">
+        <is>
+          <t>1.05%→0.77%</t>
+        </is>
+      </c>
+      <c r="K147" s="13" t="inlineStr">
+        <is>
+          <t>28→21</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="17" t="n"/>
+      <c r="B148" s="17" t="n"/>
+      <c r="C148" s="17" t="n"/>
+      <c r="D148" s="17" t="n"/>
+      <c r="E148" s="17" t="n"/>
+      <c r="G148" s="14" t="inlineStr">
+        <is>
+          <t>서진시스템</t>
+        </is>
+      </c>
+      <c r="H148" s="15" t="n">
+        <v>-7</v>
+      </c>
+      <c r="I148" s="15" t="n">
+        <v>-93266316</v>
+      </c>
+      <c r="J148" s="16" t="inlineStr">
+        <is>
+          <t>4.02%→3.58%</t>
+        </is>
+      </c>
+      <c r="K148" s="13" t="inlineStr">
+        <is>
+          <t>82→75</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="17" t="n"/>
+      <c r="B149" s="17" t="n"/>
+      <c r="C149" s="17" t="n"/>
+      <c r="D149" s="17" t="n"/>
+      <c r="E149" s="17" t="n"/>
+      <c r="G149" s="14" t="inlineStr">
+        <is>
+          <t>피에스케이</t>
+        </is>
+      </c>
+      <c r="H149" s="15" t="n">
+        <v>-6</v>
+      </c>
+      <c r="I149" s="15" t="n">
+        <v>-277950196</v>
+      </c>
+      <c r="J149" s="16" t="inlineStr">
+        <is>
+          <t>1.71%→0.66%</t>
+        </is>
+      </c>
+      <c r="K149" s="13" t="inlineStr">
+        <is>
+          <t>10→4</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="17" t="n"/>
+      <c r="B150" s="17" t="n"/>
+      <c r="C150" s="17" t="n"/>
+      <c r="D150" s="17" t="n"/>
+      <c r="E150" s="17" t="n"/>
+      <c r="G150" s="14" t="inlineStr">
+        <is>
+          <t>인텔리안테크</t>
+        </is>
+      </c>
+      <c r="H150" s="15" t="n">
+        <v>-5</v>
+      </c>
+      <c r="I150" s="15" t="n">
+        <v>-109012577</v>
+      </c>
+      <c r="J150" s="16" t="inlineStr">
+        <is>
+          <t>0.80%→0.39%</t>
+        </is>
+      </c>
+      <c r="K150" s="13" t="inlineStr">
+        <is>
+          <t>10→5</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="17" t="n"/>
+      <c r="B151" s="17" t="n"/>
+      <c r="C151" s="17" t="n"/>
+      <c r="D151" s="17" t="n"/>
+      <c r="E151" s="17" t="n"/>
+      <c r="G151" s="14" t="inlineStr">
+        <is>
+          <t>펌텍코리아</t>
+        </is>
+      </c>
+      <c r="H151" s="15" t="n">
         <v>-4</v>
       </c>
-      <c r="I126" s="15" t="n">
-        <v>-162915961</v>
-      </c>
-      <c r="J126" s="16" t="inlineStr">
-        <is>
-          <t>2.45%→2.13%</t>
-        </is>
-      </c>
-      <c r="K126" s="13" t="inlineStr">
-        <is>
-          <t>46→42</t>
-        </is>
-      </c>
-    </row>
-    <row r="128" ht="19" customHeight="1">
-      <c r="A128" s="18" t="inlineStr">
-        <is>
-          <t>■ TIGER 코스닥액티브  (미래에셋)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B128" s="19" t="n"/>
-      <c r="C128" s="19" t="n"/>
-      <c r="D128" s="19" t="n"/>
-      <c r="E128" s="19" t="n"/>
-      <c r="F128" s="19" t="n"/>
-      <c r="G128" s="19" t="n"/>
-      <c r="H128" s="19" t="n"/>
-      <c r="I128" s="19" t="n"/>
-      <c r="J128" s="19" t="n"/>
-      <c r="K128" s="19" t="n"/>
-    </row>
-    <row r="130" ht="19" customHeight="1">
-      <c r="A130" s="18" t="inlineStr">
-        <is>
-          <t>■ MIDAS 코스닥액티브  (마이다스)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B130" s="19" t="n"/>
-      <c r="C130" s="19" t="n"/>
-      <c r="D130" s="19" t="n"/>
-      <c r="E130" s="19" t="n"/>
-      <c r="F130" s="19" t="n"/>
-      <c r="G130" s="19" t="n"/>
-      <c r="H130" s="19" t="n"/>
-      <c r="I130" s="19" t="n"/>
-      <c r="J130" s="19" t="n"/>
-      <c r="K130" s="19" t="n"/>
+      <c r="I151" s="15" t="n">
+        <v>-116620082</v>
+      </c>
+      <c r="J151" s="16" t="inlineStr">
+        <is>
+          <t>3.86%→3.34%</t>
+        </is>
+      </c>
+      <c r="K151" s="13" t="inlineStr">
+        <is>
+          <t>36→32</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="17" t="n"/>
+      <c r="B152" s="17" t="n"/>
+      <c r="C152" s="17" t="n"/>
+      <c r="D152" s="17" t="n"/>
+      <c r="E152" s="17" t="n"/>
+      <c r="G152" s="14" t="inlineStr">
+        <is>
+          <t>한라IMS</t>
+        </is>
+      </c>
+      <c r="H152" s="15" t="n">
+        <v>-3</v>
+      </c>
+      <c r="I152" s="15" t="n">
+        <v>-17493012</v>
+      </c>
+      <c r="J152" s="16" t="inlineStr">
+        <is>
+          <t>0.36%→0.29%</t>
+        </is>
+      </c>
+      <c r="K152" s="13" t="inlineStr">
+        <is>
+          <t>17→14</t>
+        </is>
+      </c>
+    </row>
+    <row r="154" ht="19" customHeight="1">
+      <c r="A154" s="3" t="inlineStr">
+        <is>
+          <t>■ MIDAS 코스닥액티브  (마이다스)      순자산 ≈ 53억   ·   현금 1억(1.8%)      오늘 2026-10-27  vs  5일전 2026-10-20      매수 4종목  /  매도 3종목</t>
+        </is>
+      </c>
+      <c r="B154" s="4" t="n"/>
+      <c r="C154" s="4" t="n"/>
+      <c r="D154" s="4" t="n"/>
+      <c r="E154" s="4" t="n"/>
+      <c r="F154" s="4" t="n"/>
+      <c r="G154" s="4" t="n"/>
+      <c r="H154" s="4" t="n"/>
+      <c r="I154" s="4" t="n"/>
+      <c r="J154" s="4" t="n"/>
+      <c r="K154" s="4" t="n"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B155" s="6" t="n"/>
+      <c r="C155" s="6" t="n"/>
+      <c r="D155" s="6" t="n"/>
+      <c r="E155" s="6" t="n"/>
+      <c r="G155" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H155" s="8" t="n"/>
+      <c r="I155" s="8" t="n"/>
+      <c r="J155" s="8" t="n"/>
+      <c r="K155" s="8" t="n"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B156" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C156" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D156" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E156" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G156" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H156" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I156" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J156" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K156" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="10" t="inlineStr">
+        <is>
+          <t>큐리언트  (신규)</t>
+        </is>
+      </c>
+      <c r="B157" s="11" t="n">
+        <v>176</v>
+      </c>
+      <c r="C157" s="11" t="n">
+        <v>26850560</v>
+      </c>
+      <c r="D157" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→0.52%</t>
+        </is>
+      </c>
+      <c r="E157" s="13" t="inlineStr">
+        <is>
+          <t>0→176</t>
+        </is>
+      </c>
+      <c r="G157" s="14" t="inlineStr">
+        <is>
+          <t>엘티씨</t>
+        </is>
+      </c>
+      <c r="H157" s="15" t="n">
+        <v>-98</v>
+      </c>
+      <c r="I157" s="15" t="n">
+        <v>-25166400</v>
+      </c>
+      <c r="J157" s="16" t="inlineStr">
+        <is>
+          <t>3.40%→2.90%</t>
+        </is>
+      </c>
+      <c r="K157" s="13" t="inlineStr">
+        <is>
+          <t>683→585</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="10" t="inlineStr">
+        <is>
+          <t>파두</t>
+        </is>
+      </c>
+      <c r="B158" s="11" t="n">
+        <v>56</v>
+      </c>
+      <c r="C158" s="11" t="n">
+        <v>20070400</v>
+      </c>
+      <c r="D158" s="12" t="inlineStr">
+        <is>
+          <t>3.12%→3.50%</t>
+        </is>
+      </c>
+      <c r="E158" s="13" t="inlineStr">
+        <is>
+          <t>449→505</t>
+        </is>
+      </c>
+      <c r="G158" s="14" t="inlineStr">
+        <is>
+          <t>테스</t>
+        </is>
+      </c>
+      <c r="H158" s="15" t="n">
+        <v>-28</v>
+      </c>
+      <c r="I158" s="15" t="n">
+        <v>-23564800</v>
+      </c>
+      <c r="J158" s="16" t="inlineStr">
+        <is>
+          <t>4.52%→4.05%</t>
+        </is>
+      </c>
+      <c r="K158" s="13" t="inlineStr">
+        <is>
+          <t>277→249</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="10" t="inlineStr">
+        <is>
+          <t>대주전자재료</t>
+        </is>
+      </c>
+      <c r="B159" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="C159" s="11" t="n">
+        <v>8812800</v>
+      </c>
+      <c r="D159" s="12" t="inlineStr">
+        <is>
+          <t>2.52%→2.68%</t>
+        </is>
+      </c>
+      <c r="E159" s="13" t="inlineStr">
+        <is>
+          <t>177→189</t>
+        </is>
+      </c>
+      <c r="G159" s="14" t="inlineStr">
+        <is>
+          <t>피에스케이홀딩스</t>
+        </is>
+      </c>
+      <c r="H159" s="15" t="n">
+        <v>-19</v>
+      </c>
+      <c r="I159" s="15" t="n">
+        <v>-23970400</v>
+      </c>
+      <c r="J159" s="16" t="inlineStr">
+        <is>
+          <t>4.94%→4.46%</t>
+        </is>
+      </c>
+      <c r="K159" s="13" t="inlineStr">
+        <is>
+          <t>202→183</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="10" t="inlineStr">
+        <is>
+          <t>이오테크닉스</t>
+        </is>
+      </c>
+      <c r="B160" s="11" t="n">
+        <v>11</v>
+      </c>
+      <c r="C160" s="11" t="n">
+        <v>33352000</v>
+      </c>
+      <c r="D160" s="12" t="inlineStr">
+        <is>
+          <t>5.94%→6.56%</t>
+        </is>
+      </c>
+      <c r="E160" s="13" t="inlineStr">
+        <is>
+          <t>101→112</t>
+        </is>
+      </c>
+      <c r="G160" s="17" t="n"/>
+      <c r="H160" s="17" t="n"/>
+      <c r="I160" s="17" t="n"/>
+      <c r="J160" s="17" t="n"/>
+      <c r="K160" s="17" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="24">
-    <mergeCell ref="A130:K130"/>
+  <mergeCells count="30">
+    <mergeCell ref="A114:E114"/>
+    <mergeCell ref="G155:K155"/>
     <mergeCell ref="A24:K24"/>
-    <mergeCell ref="A107:K107"/>
     <mergeCell ref="A45:E45"/>
     <mergeCell ref="A103:K103"/>
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="A79:K79"/>
     <mergeCell ref="A88:K88"/>
     <mergeCell ref="A25:E25"/>
-    <mergeCell ref="A108:E108"/>
-    <mergeCell ref="A128:K128"/>
     <mergeCell ref="A89:E89"/>
     <mergeCell ref="A80:E80"/>
     <mergeCell ref="A105:K105"/>
     <mergeCell ref="A3:K3"/>
-    <mergeCell ref="G108:K108"/>
+    <mergeCell ref="A154:K154"/>
+    <mergeCell ref="A113:K113"/>
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="G89:K89"/>
     <mergeCell ref="G80:K80"/>
+    <mergeCell ref="G114:K114"/>
     <mergeCell ref="G45:K45"/>
+    <mergeCell ref="A135:E135"/>
     <mergeCell ref="G4:K4"/>
+    <mergeCell ref="A106:E106"/>
+    <mergeCell ref="G135:K135"/>
     <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A134:K134"/>
     <mergeCell ref="G25:K25"/>
+    <mergeCell ref="A155:E155"/>
+    <mergeCell ref="G106:K106"/>
     <mergeCell ref="A44:K44"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/reports/pdf_rolling5_20261027.xlsx
+++ b/reports/pdf_rolling5_20261027.xlsx
@@ -834,23 +834,23 @@
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>에코프로에이치엔</t>
+          <t>프로티나  (신규)</t>
         </is>
       </c>
       <c r="B10" s="11" t="n">
         <v>104</v>
       </c>
       <c r="C10" s="11" t="n">
-        <v>2308129525</v>
+        <v>4812475878</v>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
-          <t>0.22%→0.77%</t>
+          <t>0.00%→1.17%</t>
         </is>
       </c>
       <c r="E10" s="13" t="inlineStr">
         <is>
-          <t>38→142</t>
+          <t>0→104</t>
         </is>
       </c>
       <c r="G10" s="14" t="inlineStr">
@@ -878,23 +878,23 @@
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>프로티나  (신규)</t>
+          <t>에코프로에이치엔</t>
         </is>
       </c>
       <c r="B11" s="11" t="n">
         <v>104</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>4812475878</v>
+        <v>2308129525</v>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>0.00%→1.17%</t>
+          <t>0.22%→0.77%</t>
         </is>
       </c>
       <c r="E11" s="13" t="inlineStr">
         <is>
-          <t>0→104</t>
+          <t>38→142</t>
         </is>
       </c>
       <c r="G11" s="14" t="inlineStr">
@@ -1010,23 +1010,23 @@
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>씨메스로보틱스</t>
         </is>
       </c>
       <c r="B14" s="11" t="n">
         <v>29</v>
       </c>
       <c r="C14" s="11" t="n">
-        <v>1174917766</v>
+        <v>412373098</v>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>0.56%→0.82%</t>
+          <t>0.13%→0.23%</t>
         </is>
       </c>
       <c r="E14" s="13" t="inlineStr">
         <is>
-          <t>54→83</t>
+          <t>37→66</t>
         </is>
       </c>
       <c r="G14" s="14" t="inlineStr">
@@ -1054,23 +1054,23 @@
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>씨메스로보틱스</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="B15" s="11" t="n">
         <v>29</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>412373098</v>
+        <v>1174917766</v>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>0.13%→0.23%</t>
+          <t>0.56%→0.82%</t>
         </is>
       </c>
       <c r="E15" s="13" t="inlineStr">
         <is>
-          <t>37→66</t>
+          <t>54→83</t>
         </is>
       </c>
       <c r="G15" s="14" t="inlineStr">
@@ -1186,23 +1186,23 @@
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>파두</t>
+          <t>파크시스템스</t>
         </is>
       </c>
       <c r="B18" s="11" t="n">
         <v>12</v>
       </c>
       <c r="C18" s="11" t="n">
-        <v>533836875</v>
+        <v>2657268375</v>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>0.42%→0.50%</t>
+          <t>1.43%→1.99%</t>
         </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
-          <t>34→46</t>
+          <t>25→37</t>
         </is>
       </c>
       <c r="G18" s="17" t="n"/>
@@ -1214,23 +1214,23 @@
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>원익머트리얼즈</t>
+          <t>파두</t>
         </is>
       </c>
       <c r="B19" s="11" t="n">
         <v>12</v>
       </c>
       <c r="C19" s="11" t="n">
-        <v>393228055</v>
+        <v>533836875</v>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>1.43%→1.47%</t>
+          <t>0.42%→0.50%</t>
         </is>
       </c>
       <c r="E19" s="13" t="inlineStr">
         <is>
-          <t>173→185</t>
+          <t>34→46</t>
         </is>
       </c>
       <c r="G19" s="17" t="n"/>
@@ -1242,23 +1242,23 @@
     <row r="20">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>파크시스템스</t>
+          <t>원익머트리얼즈</t>
         </is>
       </c>
       <c r="B20" s="11" t="n">
         <v>12</v>
       </c>
       <c r="C20" s="11" t="n">
-        <v>2657268375</v>
+        <v>393228055</v>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
-          <t>1.43%→1.99%</t>
+          <t>1.43%→1.47%</t>
         </is>
       </c>
       <c r="E20" s="13" t="inlineStr">
         <is>
-          <t>25→37</t>
+          <t>173→185</t>
         </is>
       </c>
       <c r="G20" s="17" t="n"/>
@@ -1828,23 +1828,23 @@
       <c r="E37" s="17" t="n"/>
       <c r="G37" s="14" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>에스티팜</t>
         </is>
       </c>
       <c r="H37" s="15" t="n">
         <v>-22</v>
       </c>
       <c r="I37" s="15" t="n">
-        <v>-2711311990</v>
+        <v>-1045538611</v>
       </c>
       <c r="J37" s="16" t="inlineStr">
         <is>
-          <t>3.83%→2.48%</t>
+          <t>7.45%→7.13%</t>
         </is>
       </c>
       <c r="K37" s="13" t="inlineStr">
         <is>
-          <t>81→59</t>
+          <t>462→440</t>
         </is>
       </c>
     </row>
@@ -1856,23 +1856,23 @@
       <c r="E38" s="17" t="n"/>
       <c r="G38" s="14" t="inlineStr">
         <is>
-          <t>에스티팜</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="H38" s="15" t="n">
         <v>-22</v>
       </c>
       <c r="I38" s="15" t="n">
-        <v>-1045538611</v>
+        <v>-2711311990</v>
       </c>
       <c r="J38" s="16" t="inlineStr">
         <is>
-          <t>7.45%→7.13%</t>
+          <t>3.83%→2.48%</t>
         </is>
       </c>
       <c r="K38" s="13" t="inlineStr">
         <is>
-          <t>462→440</t>
+          <t>81→59</t>
         </is>
       </c>
     </row>
@@ -2321,23 +2321,23 @@
       </c>
       <c r="G52" s="14" t="inlineStr">
         <is>
-          <t>필옵틱스</t>
+          <t>한선엔지니어링</t>
         </is>
       </c>
       <c r="H52" s="15" t="n">
         <v>-112</v>
       </c>
       <c r="I52" s="15" t="n">
-        <v>-2061201705</v>
+        <v>-948301072</v>
       </c>
       <c r="J52" s="16" t="inlineStr">
         <is>
-          <t>2.12%→1.00%</t>
+          <t>1.01%→0.43%</t>
         </is>
       </c>
       <c r="K52" s="13" t="inlineStr">
         <is>
-          <t>220→108</t>
+          <t>213→101</t>
         </is>
       </c>
     </row>
@@ -2365,23 +2365,23 @@
       </c>
       <c r="G53" s="14" t="inlineStr">
         <is>
-          <t>한선엔지니어링</t>
+          <t>필옵틱스</t>
         </is>
       </c>
       <c r="H53" s="15" t="n">
         <v>-112</v>
       </c>
       <c r="I53" s="15" t="n">
-        <v>-948301072</v>
+        <v>-2061201705</v>
       </c>
       <c r="J53" s="16" t="inlineStr">
         <is>
-          <t>1.01%→0.43%</t>
+          <t>2.12%→1.00%</t>
         </is>
       </c>
       <c r="K53" s="13" t="inlineStr">
         <is>
-          <t>213→101</t>
+          <t>220→108</t>
         </is>
       </c>
     </row>
@@ -2520,18 +2520,18 @@
     <row r="57">
       <c r="A57" s="10" t="inlineStr">
         <is>
-          <t>엘티씨  (신규)</t>
+          <t>디케이티  (신규)</t>
         </is>
       </c>
       <c r="B57" s="11" t="n">
         <v>99</v>
       </c>
       <c r="C57" s="11" t="n">
-        <v>2103768275</v>
+        <v>1612233631</v>
       </c>
       <c r="D57" s="12" t="inlineStr">
         <is>
-          <t>0.00%→1.06%</t>
+          <t>0.00%→0.81%</t>
         </is>
       </c>
       <c r="E57" s="13" t="inlineStr">
@@ -2564,18 +2564,18 @@
     <row r="58">
       <c r="A58" s="10" t="inlineStr">
         <is>
-          <t>디케이티  (신규)</t>
+          <t>엘티씨  (신규)</t>
         </is>
       </c>
       <c r="B58" s="11" t="n">
         <v>99</v>
       </c>
       <c r="C58" s="11" t="n">
-        <v>1612233631</v>
+        <v>2103768275</v>
       </c>
       <c r="D58" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.81%</t>
+          <t>0.00%→1.06%</t>
         </is>
       </c>
       <c r="E58" s="13" t="inlineStr">
@@ -2981,23 +2981,23 @@
       </c>
       <c r="G67" s="14" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>대주전자재료</t>
         </is>
       </c>
       <c r="H67" s="15" t="n">
         <v>-26</v>
       </c>
       <c r="I67" s="15" t="n">
-        <v>-4148088992</v>
+        <v>-1580060454</v>
       </c>
       <c r="J67" s="16" t="inlineStr">
         <is>
-          <t>4.69%→2.73%</t>
+          <t>1.57%→0.73%</t>
         </is>
       </c>
       <c r="K67" s="13" t="inlineStr">
         <is>
-          <t>60→34</t>
+          <t>50→24</t>
         </is>
       </c>
     </row>
@@ -3009,23 +3009,23 @@
       <c r="E68" s="17" t="n"/>
       <c r="G68" s="14" t="inlineStr">
         <is>
-          <t>대주전자재료</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="H68" s="15" t="n">
         <v>-26</v>
       </c>
       <c r="I68" s="15" t="n">
-        <v>-1580060454</v>
+        <v>-4148088992</v>
       </c>
       <c r="J68" s="16" t="inlineStr">
         <is>
-          <t>1.57%→0.73%</t>
+          <t>4.69%→2.73%</t>
         </is>
       </c>
       <c r="K68" s="13" t="inlineStr">
         <is>
-          <t>50→24</t>
+          <t>60→34</t>
         </is>
       </c>
     </row>
@@ -3177,23 +3177,23 @@
       <c r="E74" s="17" t="n"/>
       <c r="G74" s="14" t="inlineStr">
         <is>
-          <t>레인보우로보틱스</t>
+          <t>보로노이  (편출)</t>
         </is>
       </c>
       <c r="H74" s="15" t="n">
         <v>-8</v>
       </c>
       <c r="I74" s="15" t="n">
-        <v>-1840358666</v>
+        <v>-697482694</v>
       </c>
       <c r="J74" s="16" t="inlineStr">
         <is>
-          <t>2.85%→2.20%</t>
+          <t>0.29%→0.00%</t>
         </is>
       </c>
       <c r="K74" s="13" t="inlineStr">
         <is>
-          <t>27→19</t>
+          <t>8→0</t>
         </is>
       </c>
     </row>
@@ -3205,23 +3205,23 @@
       <c r="E75" s="17" t="n"/>
       <c r="G75" s="14" t="inlineStr">
         <is>
-          <t>보로노이  (편출)</t>
+          <t>레인보우로보틱스</t>
         </is>
       </c>
       <c r="H75" s="15" t="n">
         <v>-8</v>
       </c>
       <c r="I75" s="15" t="n">
-        <v>-697482694</v>
+        <v>-1840358666</v>
       </c>
       <c r="J75" s="16" t="inlineStr">
         <is>
-          <t>0.29%→0.00%</t>
+          <t>2.85%→2.20%</t>
         </is>
       </c>
       <c r="K75" s="13" t="inlineStr">
         <is>
-          <t>8→0</t>
+          <t>27→19</t>
         </is>
       </c>
     </row>
@@ -3958,23 +3958,23 @@
     <row r="98">
       <c r="A98" s="10" t="inlineStr">
         <is>
-          <t>선익시스템</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="B98" s="11" t="n">
         <v>7</v>
       </c>
       <c r="C98" s="11" t="n">
-        <v>37004800</v>
+        <v>47129600</v>
       </c>
       <c r="D98" s="12" t="inlineStr">
         <is>
-          <t>1.34%→1.49%</t>
+          <t>2.26%→2.45%</t>
         </is>
       </c>
       <c r="E98" s="13" t="inlineStr">
         <is>
-          <t>58→65</t>
+          <t>77→84</t>
         </is>
       </c>
       <c r="G98" s="14" t="inlineStr">
@@ -4002,23 +4002,23 @@
     <row r="99">
       <c r="A99" s="10" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>선익시스템</t>
         </is>
       </c>
       <c r="B99" s="11" t="n">
         <v>7</v>
       </c>
       <c r="C99" s="11" t="n">
-        <v>47129600</v>
+        <v>37004800</v>
       </c>
       <c r="D99" s="12" t="inlineStr">
         <is>
-          <t>2.26%→2.45%</t>
+          <t>1.34%→1.49%</t>
         </is>
       </c>
       <c r="E99" s="13" t="inlineStr">
         <is>
-          <t>77→84</t>
+          <t>58→65</t>
         </is>
       </c>
       <c r="G99" s="17" t="n"/>
@@ -4103,7 +4103,7 @@
     <row r="105" ht="19" customHeight="1">
       <c r="A105" s="3" t="inlineStr">
         <is>
-          <t>■ TIGER 기술이전바이오액티브  (미래에셋)      순자산 ≈ 1,035억   ·   현금 69억(6.6%)      오늘 2026-10-27  vs  5일전 2026-10-20      매수 2종목  /  매도 4종목</t>
+          <t>■ TIGER 기술이전바이오액티브  (미래에셋)      순자산 ≈ 1,035억      오늘 2026-10-27  vs  5일전 2026-10-20      매수 2종목  /  매도 4종목</t>
         </is>
       </c>
       <c r="B105" s="4" t="n"/>
@@ -4213,23 +4213,23 @@
       </c>
       <c r="G108" s="14" t="inlineStr">
         <is>
-          <t>와이바이오로직스</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="H108" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I108" s="15" t="n">
-        <v>-83708861</v>
+        <v>-537891589</v>
       </c>
       <c r="J108" s="16" t="inlineStr">
         <is>
-          <t>0.44%→0.24%</t>
+          <t>7.53%→5.01%</t>
         </is>
       </c>
       <c r="K108" s="13" t="inlineStr">
         <is>
-          <t>15→11</t>
+          <t>40→36</t>
         </is>
       </c>
     </row>
@@ -4257,23 +4257,23 @@
       </c>
       <c r="G109" s="14" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>와이바이오로직스</t>
         </is>
       </c>
       <c r="H109" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I109" s="15" t="n">
-        <v>-537891589</v>
+        <v>-83708861</v>
       </c>
       <c r="J109" s="16" t="inlineStr">
         <is>
-          <t>7.53%→5.01%</t>
+          <t>0.44%→0.24%</t>
         </is>
       </c>
       <c r="K109" s="13" t="inlineStr">
         <is>
-          <t>40→36</t>
+          <t>15→11</t>
         </is>
       </c>
     </row>
@@ -4285,23 +4285,23 @@
       <c r="E110" s="17" t="n"/>
       <c r="G110" s="14" t="inlineStr">
         <is>
-          <t>오름테라퓨틱</t>
+          <t>유한양행</t>
         </is>
       </c>
       <c r="H110" s="15" t="n">
         <v>-3</v>
       </c>
       <c r="I110" s="15" t="n">
-        <v>-100139832</v>
+        <v>-507847568</v>
       </c>
       <c r="J110" s="16" t="inlineStr">
         <is>
-          <t>0.42%→0.21%</t>
+          <t>0.00%→1.58%</t>
         </is>
       </c>
       <c r="K110" s="13" t="inlineStr">
         <is>
-          <t>9→6</t>
+          <t>12→9</t>
         </is>
       </c>
     </row>
@@ -4313,23 +4313,23 @@
       <c r="E111" s="17" t="n"/>
       <c r="G111" s="14" t="inlineStr">
         <is>
-          <t>유한양행</t>
+          <t>오름테라퓨틱</t>
         </is>
       </c>
       <c r="H111" s="15" t="n">
         <v>-3</v>
       </c>
       <c r="I111" s="15" t="n">
-        <v>-507847568</v>
+        <v>-100139832</v>
       </c>
       <c r="J111" s="16" t="inlineStr">
         <is>
-          <t>0.00%→1.58%</t>
+          <t>0.42%→0.21%</t>
         </is>
       </c>
       <c r="K111" s="13" t="inlineStr">
         <is>
-          <t>12→9</t>
+          <t>9→6</t>
         </is>
       </c>
     </row>
@@ -5074,23 +5074,23 @@
       <c r="E131" s="17" t="n"/>
       <c r="G131" s="14" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>이오테크닉스</t>
         </is>
       </c>
       <c r="H131" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I131" s="15" t="n">
-        <v>-161952077</v>
+        <v>-254688121</v>
       </c>
       <c r="J131" s="16" t="inlineStr">
         <is>
-          <t>2.45%→2.13%</t>
+          <t>4.42%→3.92%</t>
         </is>
       </c>
       <c r="K131" s="13" t="inlineStr">
         <is>
-          <t>46→42</t>
+          <t>53→49</t>
         </is>
       </c>
     </row>
@@ -5102,30 +5102,30 @@
       <c r="E132" s="17" t="n"/>
       <c r="G132" s="14" t="inlineStr">
         <is>
-          <t>이오테크닉스</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="H132" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I132" s="15" t="n">
-        <v>-254688121</v>
+        <v>-161952077</v>
       </c>
       <c r="J132" s="16" t="inlineStr">
         <is>
-          <t>4.42%→3.92%</t>
+          <t>2.45%→2.13%</t>
         </is>
       </c>
       <c r="K132" s="13" t="inlineStr">
         <is>
-          <t>53→49</t>
+          <t>46→42</t>
         </is>
       </c>
     </row>
     <row r="134" ht="19" customHeight="1">
       <c r="A134" s="3" t="inlineStr">
         <is>
-          <t>■ TIGER 코스닥액티브  (미래에셋)      순자산 ≈ 281억   ·   현금 2억(0.7%)      오늘 2026-10-27  vs  5일전 2026-10-20      매수 9종목  /  매도 16종목</t>
+          <t>■ TIGER 코스닥액티브  (미래에셋)      순자산 ≈ 281억      오늘 2026-10-27  vs  5일전 2026-10-20      매수 9종목  /  매도 16종목</t>
         </is>
       </c>
       <c r="B134" s="4" t="n"/>
@@ -5434,23 +5434,23 @@
     <row r="142">
       <c r="A142" s="10" t="inlineStr">
         <is>
-          <t>선익시스템  (신규)</t>
+          <t>알지노믹스</t>
         </is>
       </c>
       <c r="B142" s="11" t="n">
         <v>9</v>
       </c>
       <c r="C142" s="11" t="n">
-        <v>315945223</v>
+        <v>87210062</v>
       </c>
       <c r="D142" s="12" t="inlineStr">
         <is>
-          <t>0.00%→1.13%</t>
+          <t>0.75%→1.04%</t>
         </is>
       </c>
       <c r="E142" s="13" t="inlineStr">
         <is>
-          <t>0→9</t>
+          <t>21→30</t>
         </is>
       </c>
       <c r="G142" s="14" t="inlineStr">
@@ -5478,23 +5478,23 @@
     <row r="143">
       <c r="A143" s="10" t="inlineStr">
         <is>
-          <t>알지노믹스</t>
+          <t>선익시스템  (신규)</t>
         </is>
       </c>
       <c r="B143" s="11" t="n">
         <v>9</v>
       </c>
       <c r="C143" s="11" t="n">
-        <v>87210062</v>
+        <v>315945223</v>
       </c>
       <c r="D143" s="12" t="inlineStr">
         <is>
-          <t>0.75%→1.04%</t>
+          <t>0.00%→1.13%</t>
         </is>
       </c>
       <c r="E143" s="13" t="inlineStr">
         <is>
-          <t>21→30</t>
+          <t>0→9</t>
         </is>
       </c>
       <c r="G143" s="14" t="inlineStr">
@@ -5643,23 +5643,23 @@
       <c r="E147" s="17" t="n"/>
       <c r="G147" s="14" t="inlineStr">
         <is>
-          <t>오이솔루션</t>
+          <t>서진시스템</t>
         </is>
       </c>
       <c r="H147" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I147" s="15" t="n">
-        <v>-71400050</v>
+        <v>-93266316</v>
       </c>
       <c r="J147" s="16" t="inlineStr">
         <is>
-          <t>1.05%→0.77%</t>
+          <t>4.02%→3.58%</t>
         </is>
       </c>
       <c r="K147" s="13" t="inlineStr">
         <is>
-          <t>28→21</t>
+          <t>82→75</t>
         </is>
       </c>
     </row>
@@ -5671,23 +5671,23 @@
       <c r="E148" s="17" t="n"/>
       <c r="G148" s="14" t="inlineStr">
         <is>
-          <t>서진시스템</t>
+          <t>오이솔루션</t>
         </is>
       </c>
       <c r="H148" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I148" s="15" t="n">
-        <v>-93266316</v>
+        <v>-71400050</v>
       </c>
       <c r="J148" s="16" t="inlineStr">
         <is>
-          <t>4.02%→3.58%</t>
+          <t>1.05%→0.77%</t>
         </is>
       </c>
       <c r="K148" s="13" t="inlineStr">
         <is>
-          <t>82→75</t>
+          <t>28→21</t>
         </is>
       </c>
     </row>
@@ -5806,7 +5806,7 @@
     <row r="154" ht="19" customHeight="1">
       <c r="A154" s="3" t="inlineStr">
         <is>
-          <t>■ MIDAS 코스닥액티브  (마이다스)      순자산 ≈ 53억   ·   현금 1억(1.8%)      오늘 2026-10-27  vs  5일전 2026-10-20      매수 4종목  /  매도 3종목</t>
+          <t>■ MIDAS 코스닥액티브  (마이다스)      순자산 ≈ 53억      오늘 2026-10-27  vs  5일전 2026-10-20      매수 4종목  /  매도 3종목</t>
         </is>
       </c>
       <c r="B154" s="4" t="n"/>

--- a/reports/pdf_rolling5_20261027.xlsx
+++ b/reports/pdf_rolling5_20261027.xlsx
@@ -834,23 +834,23 @@
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>프로티나  (신규)</t>
+          <t>에코프로에이치엔</t>
         </is>
       </c>
       <c r="B10" s="11" t="n">
         <v>104</v>
       </c>
       <c r="C10" s="11" t="n">
-        <v>4812475878</v>
+        <v>2308129525</v>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
-          <t>0.00%→1.17%</t>
+          <t>0.22%→0.77%</t>
         </is>
       </c>
       <c r="E10" s="13" t="inlineStr">
         <is>
-          <t>0→104</t>
+          <t>38→142</t>
         </is>
       </c>
       <c r="G10" s="14" t="inlineStr">
@@ -878,23 +878,23 @@
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>에코프로에이치엔</t>
+          <t>프로티나  (신규)</t>
         </is>
       </c>
       <c r="B11" s="11" t="n">
         <v>104</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>2308129525</v>
+        <v>4812475878</v>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>0.22%→0.77%</t>
+          <t>0.00%→1.17%</t>
         </is>
       </c>
       <c r="E11" s="13" t="inlineStr">
         <is>
-          <t>38→142</t>
+          <t>0→104</t>
         </is>
       </c>
       <c r="G11" s="14" t="inlineStr">
@@ -1828,23 +1828,23 @@
       <c r="E37" s="17" t="n"/>
       <c r="G37" s="14" t="inlineStr">
         <is>
-          <t>에스티팜</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="H37" s="15" t="n">
         <v>-22</v>
       </c>
       <c r="I37" s="15" t="n">
-        <v>-1045538611</v>
+        <v>-2711311990</v>
       </c>
       <c r="J37" s="16" t="inlineStr">
         <is>
-          <t>7.45%→7.13%</t>
+          <t>3.83%→2.48%</t>
         </is>
       </c>
       <c r="K37" s="13" t="inlineStr">
         <is>
-          <t>462→440</t>
+          <t>81→59</t>
         </is>
       </c>
     </row>
@@ -1856,23 +1856,23 @@
       <c r="E38" s="17" t="n"/>
       <c r="G38" s="14" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>에스티팜</t>
         </is>
       </c>
       <c r="H38" s="15" t="n">
         <v>-22</v>
       </c>
       <c r="I38" s="15" t="n">
-        <v>-2711311990</v>
+        <v>-1045538611</v>
       </c>
       <c r="J38" s="16" t="inlineStr">
         <is>
-          <t>3.83%→2.48%</t>
+          <t>7.45%→7.13%</t>
         </is>
       </c>
       <c r="K38" s="13" t="inlineStr">
         <is>
-          <t>81→59</t>
+          <t>462→440</t>
         </is>
       </c>
     </row>
@@ -2321,23 +2321,23 @@
       </c>
       <c r="G52" s="14" t="inlineStr">
         <is>
-          <t>한선엔지니어링</t>
+          <t>필옵틱스</t>
         </is>
       </c>
       <c r="H52" s="15" t="n">
         <v>-112</v>
       </c>
       <c r="I52" s="15" t="n">
-        <v>-948301072</v>
+        <v>-2061201705</v>
       </c>
       <c r="J52" s="16" t="inlineStr">
         <is>
-          <t>1.01%→0.43%</t>
+          <t>2.12%→1.00%</t>
         </is>
       </c>
       <c r="K52" s="13" t="inlineStr">
         <is>
-          <t>213→101</t>
+          <t>220→108</t>
         </is>
       </c>
     </row>
@@ -2365,23 +2365,23 @@
       </c>
       <c r="G53" s="14" t="inlineStr">
         <is>
-          <t>필옵틱스</t>
+          <t>한선엔지니어링</t>
         </is>
       </c>
       <c r="H53" s="15" t="n">
         <v>-112</v>
       </c>
       <c r="I53" s="15" t="n">
-        <v>-2061201705</v>
+        <v>-948301072</v>
       </c>
       <c r="J53" s="16" t="inlineStr">
         <is>
-          <t>2.12%→1.00%</t>
+          <t>1.01%→0.43%</t>
         </is>
       </c>
       <c r="K53" s="13" t="inlineStr">
         <is>
-          <t>220→108</t>
+          <t>213→101</t>
         </is>
       </c>
     </row>
@@ -2520,18 +2520,18 @@
     <row r="57">
       <c r="A57" s="10" t="inlineStr">
         <is>
-          <t>디케이티  (신규)</t>
+          <t>엘티씨  (신규)</t>
         </is>
       </c>
       <c r="B57" s="11" t="n">
         <v>99</v>
       </c>
       <c r="C57" s="11" t="n">
-        <v>1612233631</v>
+        <v>2103768275</v>
       </c>
       <c r="D57" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.81%</t>
+          <t>0.00%→1.06%</t>
         </is>
       </c>
       <c r="E57" s="13" t="inlineStr">
@@ -2564,18 +2564,18 @@
     <row r="58">
       <c r="A58" s="10" t="inlineStr">
         <is>
-          <t>엘티씨  (신규)</t>
+          <t>디케이티  (신규)</t>
         </is>
       </c>
       <c r="B58" s="11" t="n">
         <v>99</v>
       </c>
       <c r="C58" s="11" t="n">
-        <v>2103768275</v>
+        <v>1612233631</v>
       </c>
       <c r="D58" s="12" t="inlineStr">
         <is>
-          <t>0.00%→1.06%</t>
+          <t>0.00%→0.81%</t>
         </is>
       </c>
       <c r="E58" s="13" t="inlineStr">
@@ -2717,23 +2717,23 @@
       </c>
       <c r="G61" s="14" t="inlineStr">
         <is>
-          <t>비츠로셀  (편출)</t>
+          <t>두산테스나</t>
         </is>
       </c>
       <c r="H61" s="15" t="n">
         <v>-50</v>
       </c>
       <c r="I61" s="15" t="n">
-        <v>-835774394</v>
+        <v>-3157737710</v>
       </c>
       <c r="J61" s="16" t="inlineStr">
         <is>
-          <t>0.35%→0.00%</t>
+          <t>2.73%→1.24%</t>
         </is>
       </c>
       <c r="K61" s="13" t="inlineStr">
         <is>
-          <t>50→0</t>
+          <t>89→39</t>
         </is>
       </c>
     </row>
@@ -2761,23 +2761,23 @@
       </c>
       <c r="G62" s="14" t="inlineStr">
         <is>
-          <t>두산테스나</t>
+          <t>비츠로셀  (편출)</t>
         </is>
       </c>
       <c r="H62" s="15" t="n">
         <v>-50</v>
       </c>
       <c r="I62" s="15" t="n">
-        <v>-3157737710</v>
+        <v>-835774394</v>
       </c>
       <c r="J62" s="16" t="inlineStr">
         <is>
-          <t>2.73%→1.24%</t>
+          <t>0.35%→0.00%</t>
         </is>
       </c>
       <c r="K62" s="13" t="inlineStr">
         <is>
-          <t>89→39</t>
+          <t>50→0</t>
         </is>
       </c>
     </row>
@@ -3958,23 +3958,23 @@
     <row r="98">
       <c r="A98" s="10" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>선익시스템</t>
         </is>
       </c>
       <c r="B98" s="11" t="n">
         <v>7</v>
       </c>
       <c r="C98" s="11" t="n">
-        <v>47129600</v>
+        <v>37004800</v>
       </c>
       <c r="D98" s="12" t="inlineStr">
         <is>
-          <t>2.26%→2.45%</t>
+          <t>1.34%→1.49%</t>
         </is>
       </c>
       <c r="E98" s="13" t="inlineStr">
         <is>
-          <t>77→84</t>
+          <t>58→65</t>
         </is>
       </c>
       <c r="G98" s="14" t="inlineStr">
@@ -4002,23 +4002,23 @@
     <row r="99">
       <c r="A99" s="10" t="inlineStr">
         <is>
-          <t>선익시스템</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="B99" s="11" t="n">
         <v>7</v>
       </c>
       <c r="C99" s="11" t="n">
-        <v>37004800</v>
+        <v>47129600</v>
       </c>
       <c r="D99" s="12" t="inlineStr">
         <is>
-          <t>1.34%→1.49%</t>
+          <t>2.26%→2.45%</t>
         </is>
       </c>
       <c r="E99" s="13" t="inlineStr">
         <is>
-          <t>58→65</t>
+          <t>77→84</t>
         </is>
       </c>
       <c r="G99" s="17" t="n"/>
@@ -4285,23 +4285,23 @@
       <c r="E110" s="17" t="n"/>
       <c r="G110" s="14" t="inlineStr">
         <is>
-          <t>유한양행</t>
+          <t>오름테라퓨틱</t>
         </is>
       </c>
       <c r="H110" s="15" t="n">
         <v>-3</v>
       </c>
       <c r="I110" s="15" t="n">
-        <v>-507847568</v>
+        <v>-100139832</v>
       </c>
       <c r="J110" s="16" t="inlineStr">
         <is>
-          <t>0.00%→1.58%</t>
+          <t>0.42%→0.21%</t>
         </is>
       </c>
       <c r="K110" s="13" t="inlineStr">
         <is>
-          <t>12→9</t>
+          <t>9→6</t>
         </is>
       </c>
     </row>
@@ -4313,23 +4313,23 @@
       <c r="E111" s="17" t="n"/>
       <c r="G111" s="14" t="inlineStr">
         <is>
-          <t>오름테라퓨틱</t>
+          <t>유한양행</t>
         </is>
       </c>
       <c r="H111" s="15" t="n">
         <v>-3</v>
       </c>
       <c r="I111" s="15" t="n">
-        <v>-100139832</v>
+        <v>-507847568</v>
       </c>
       <c r="J111" s="16" t="inlineStr">
         <is>
-          <t>0.42%→0.21%</t>
+          <t>0.00%→1.58%</t>
         </is>
       </c>
       <c r="K111" s="13" t="inlineStr">
         <is>
-          <t>9→6</t>
+          <t>12→9</t>
         </is>
       </c>
     </row>
@@ -5279,23 +5279,23 @@
       </c>
       <c r="G138" s="14" t="inlineStr">
         <is>
-          <t>피엠티</t>
+          <t>덕산하이메탈</t>
         </is>
       </c>
       <c r="H138" s="15" t="n">
         <v>-50</v>
       </c>
       <c r="I138" s="15" t="n">
-        <v>-67468798</v>
+        <v>-216325153</v>
       </c>
       <c r="J138" s="16" t="inlineStr">
         <is>
-          <t>0.26%→0.01%</t>
+          <t>1.43%→0.62%</t>
         </is>
       </c>
       <c r="K138" s="13" t="inlineStr">
         <is>
-          <t>53→3</t>
+          <t>90→40</t>
         </is>
       </c>
     </row>
@@ -5323,23 +5323,23 @@
       </c>
       <c r="G139" s="14" t="inlineStr">
         <is>
-          <t>덕산하이메탈</t>
+          <t>피엠티</t>
         </is>
       </c>
       <c r="H139" s="15" t="n">
         <v>-50</v>
       </c>
       <c r="I139" s="15" t="n">
-        <v>-216325153</v>
+        <v>-67468798</v>
       </c>
       <c r="J139" s="16" t="inlineStr">
         <is>
-          <t>1.43%→0.62%</t>
+          <t>0.26%→0.01%</t>
         </is>
       </c>
       <c r="K139" s="13" t="inlineStr">
         <is>
-          <t>90→40</t>
+          <t>53→3</t>
         </is>
       </c>
     </row>
@@ -5434,23 +5434,23 @@
     <row r="142">
       <c r="A142" s="10" t="inlineStr">
         <is>
-          <t>알지노믹스</t>
+          <t>선익시스템  (신규)</t>
         </is>
       </c>
       <c r="B142" s="11" t="n">
         <v>9</v>
       </c>
       <c r="C142" s="11" t="n">
-        <v>87210062</v>
+        <v>315945223</v>
       </c>
       <c r="D142" s="12" t="inlineStr">
         <is>
-          <t>0.75%→1.04%</t>
+          <t>0.00%→1.13%</t>
         </is>
       </c>
       <c r="E142" s="13" t="inlineStr">
         <is>
-          <t>21→30</t>
+          <t>0→9</t>
         </is>
       </c>
       <c r="G142" s="14" t="inlineStr">
@@ -5478,23 +5478,23 @@
     <row r="143">
       <c r="A143" s="10" t="inlineStr">
         <is>
-          <t>선익시스템  (신규)</t>
+          <t>알지노믹스</t>
         </is>
       </c>
       <c r="B143" s="11" t="n">
         <v>9</v>
       </c>
       <c r="C143" s="11" t="n">
-        <v>315945223</v>
+        <v>87210062</v>
       </c>
       <c r="D143" s="12" t="inlineStr">
         <is>
-          <t>0.00%→1.13%</t>
+          <t>0.75%→1.04%</t>
         </is>
       </c>
       <c r="E143" s="13" t="inlineStr">
         <is>
-          <t>0→9</t>
+          <t>21→30</t>
         </is>
       </c>
       <c r="G143" s="14" t="inlineStr">

--- a/reports/pdf_rolling5_20261027.xlsx
+++ b/reports/pdf_rolling5_20261027.xlsx
@@ -1010,23 +1010,23 @@
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>씨메스로보틱스</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="B14" s="11" t="n">
         <v>29</v>
       </c>
       <c r="C14" s="11" t="n">
-        <v>412373098</v>
+        <v>1174917766</v>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>0.13%→0.23%</t>
+          <t>0.56%→0.82%</t>
         </is>
       </c>
       <c r="E14" s="13" t="inlineStr">
         <is>
-          <t>37→66</t>
+          <t>54→83</t>
         </is>
       </c>
       <c r="G14" s="14" t="inlineStr">
@@ -1054,23 +1054,23 @@
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>씨메스로보틱스</t>
         </is>
       </c>
       <c r="B15" s="11" t="n">
         <v>29</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>1174917766</v>
+        <v>412373098</v>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>0.56%→0.82%</t>
+          <t>0.13%→0.23%</t>
         </is>
       </c>
       <c r="E15" s="13" t="inlineStr">
         <is>
-          <t>54→83</t>
+          <t>37→66</t>
         </is>
       </c>
       <c r="G15" s="14" t="inlineStr">
@@ -1186,23 +1186,23 @@
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>파크시스템스</t>
+          <t>원익머트리얼즈</t>
         </is>
       </c>
       <c r="B18" s="11" t="n">
         <v>12</v>
       </c>
       <c r="C18" s="11" t="n">
-        <v>2657268375</v>
+        <v>393228055</v>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>1.43%→1.99%</t>
+          <t>1.43%→1.47%</t>
         </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
-          <t>25→37</t>
+          <t>173→185</t>
         </is>
       </c>
       <c r="G18" s="17" t="n"/>
@@ -1214,23 +1214,23 @@
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>파두</t>
+          <t>파크시스템스</t>
         </is>
       </c>
       <c r="B19" s="11" t="n">
         <v>12</v>
       </c>
       <c r="C19" s="11" t="n">
-        <v>533836875</v>
+        <v>2657268375</v>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>0.42%→0.50%</t>
+          <t>1.43%→1.99%</t>
         </is>
       </c>
       <c r="E19" s="13" t="inlineStr">
         <is>
-          <t>34→46</t>
+          <t>25→37</t>
         </is>
       </c>
       <c r="G19" s="17" t="n"/>
@@ -1242,23 +1242,23 @@
     <row r="20">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>원익머트리얼즈</t>
+          <t>파두</t>
         </is>
       </c>
       <c r="B20" s="11" t="n">
         <v>12</v>
       </c>
       <c r="C20" s="11" t="n">
-        <v>393228055</v>
+        <v>533836875</v>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
-          <t>1.43%→1.47%</t>
+          <t>0.42%→0.50%</t>
         </is>
       </c>
       <c r="E20" s="13" t="inlineStr">
         <is>
-          <t>173→185</t>
+          <t>34→46</t>
         </is>
       </c>
       <c r="G20" s="17" t="n"/>
@@ -2520,18 +2520,18 @@
     <row r="57">
       <c r="A57" s="10" t="inlineStr">
         <is>
-          <t>엘티씨  (신규)</t>
+          <t>디케이티  (신규)</t>
         </is>
       </c>
       <c r="B57" s="11" t="n">
         <v>99</v>
       </c>
       <c r="C57" s="11" t="n">
-        <v>2103768275</v>
+        <v>1612233631</v>
       </c>
       <c r="D57" s="12" t="inlineStr">
         <is>
-          <t>0.00%→1.06%</t>
+          <t>0.00%→0.81%</t>
         </is>
       </c>
       <c r="E57" s="13" t="inlineStr">
@@ -2564,18 +2564,18 @@
     <row r="58">
       <c r="A58" s="10" t="inlineStr">
         <is>
-          <t>디케이티  (신규)</t>
+          <t>엘티씨  (신규)</t>
         </is>
       </c>
       <c r="B58" s="11" t="n">
         <v>99</v>
       </c>
       <c r="C58" s="11" t="n">
-        <v>1612233631</v>
+        <v>2103768275</v>
       </c>
       <c r="D58" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.81%</t>
+          <t>0.00%→1.06%</t>
         </is>
       </c>
       <c r="E58" s="13" t="inlineStr">
@@ -2981,23 +2981,23 @@
       </c>
       <c r="G67" s="14" t="inlineStr">
         <is>
-          <t>대주전자재료</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="H67" s="15" t="n">
         <v>-26</v>
       </c>
       <c r="I67" s="15" t="n">
-        <v>-1580060454</v>
+        <v>-4148088992</v>
       </c>
       <c r="J67" s="16" t="inlineStr">
         <is>
-          <t>1.57%→0.73%</t>
+          <t>4.69%→2.73%</t>
         </is>
       </c>
       <c r="K67" s="13" t="inlineStr">
         <is>
-          <t>50→24</t>
+          <t>60→34</t>
         </is>
       </c>
     </row>
@@ -3009,23 +3009,23 @@
       <c r="E68" s="17" t="n"/>
       <c r="G68" s="14" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>대주전자재료</t>
         </is>
       </c>
       <c r="H68" s="15" t="n">
         <v>-26</v>
       </c>
       <c r="I68" s="15" t="n">
-        <v>-4148088992</v>
+        <v>-1580060454</v>
       </c>
       <c r="J68" s="16" t="inlineStr">
         <is>
-          <t>4.69%→2.73%</t>
+          <t>1.57%→0.73%</t>
         </is>
       </c>
       <c r="K68" s="13" t="inlineStr">
         <is>
-          <t>60→34</t>
+          <t>50→24</t>
         </is>
       </c>
     </row>
@@ -3177,23 +3177,23 @@
       <c r="E74" s="17" t="n"/>
       <c r="G74" s="14" t="inlineStr">
         <is>
-          <t>보로노이  (편출)</t>
+          <t>레인보우로보틱스</t>
         </is>
       </c>
       <c r="H74" s="15" t="n">
         <v>-8</v>
       </c>
       <c r="I74" s="15" t="n">
-        <v>-697482694</v>
+        <v>-1840358666</v>
       </c>
       <c r="J74" s="16" t="inlineStr">
         <is>
-          <t>0.29%→0.00%</t>
+          <t>2.85%→2.20%</t>
         </is>
       </c>
       <c r="K74" s="13" t="inlineStr">
         <is>
-          <t>8→0</t>
+          <t>27→19</t>
         </is>
       </c>
     </row>
@@ -3205,23 +3205,23 @@
       <c r="E75" s="17" t="n"/>
       <c r="G75" s="14" t="inlineStr">
         <is>
-          <t>레인보우로보틱스</t>
+          <t>보로노이  (편출)</t>
         </is>
       </c>
       <c r="H75" s="15" t="n">
         <v>-8</v>
       </c>
       <c r="I75" s="15" t="n">
-        <v>-1840358666</v>
+        <v>-697482694</v>
       </c>
       <c r="J75" s="16" t="inlineStr">
         <is>
-          <t>2.85%→2.20%</t>
+          <t>0.29%→0.00%</t>
         </is>
       </c>
       <c r="K75" s="13" t="inlineStr">
         <is>
-          <t>27→19</t>
+          <t>8→0</t>
         </is>
       </c>
     </row>
@@ -3958,23 +3958,23 @@
     <row r="98">
       <c r="A98" s="10" t="inlineStr">
         <is>
-          <t>선익시스템</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="B98" s="11" t="n">
         <v>7</v>
       </c>
       <c r="C98" s="11" t="n">
-        <v>37004800</v>
+        <v>47129600</v>
       </c>
       <c r="D98" s="12" t="inlineStr">
         <is>
-          <t>1.34%→1.49%</t>
+          <t>2.26%→2.45%</t>
         </is>
       </c>
       <c r="E98" s="13" t="inlineStr">
         <is>
-          <t>58→65</t>
+          <t>77→84</t>
         </is>
       </c>
       <c r="G98" s="14" t="inlineStr">
@@ -4002,23 +4002,23 @@
     <row r="99">
       <c r="A99" s="10" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>선익시스템</t>
         </is>
       </c>
       <c r="B99" s="11" t="n">
         <v>7</v>
       </c>
       <c r="C99" s="11" t="n">
-        <v>47129600</v>
+        <v>37004800</v>
       </c>
       <c r="D99" s="12" t="inlineStr">
         <is>
-          <t>2.26%→2.45%</t>
+          <t>1.34%→1.49%</t>
         </is>
       </c>
       <c r="E99" s="13" t="inlineStr">
         <is>
-          <t>77→84</t>
+          <t>58→65</t>
         </is>
       </c>
       <c r="G99" s="17" t="n"/>
@@ -5434,23 +5434,23 @@
     <row r="142">
       <c r="A142" s="10" t="inlineStr">
         <is>
-          <t>선익시스템  (신규)</t>
+          <t>알지노믹스</t>
         </is>
       </c>
       <c r="B142" s="11" t="n">
         <v>9</v>
       </c>
       <c r="C142" s="11" t="n">
-        <v>315945223</v>
+        <v>87210062</v>
       </c>
       <c r="D142" s="12" t="inlineStr">
         <is>
-          <t>0.00%→1.13%</t>
+          <t>0.75%→1.04%</t>
         </is>
       </c>
       <c r="E142" s="13" t="inlineStr">
         <is>
-          <t>0→9</t>
+          <t>21→30</t>
         </is>
       </c>
       <c r="G142" s="14" t="inlineStr">
@@ -5478,23 +5478,23 @@
     <row r="143">
       <c r="A143" s="10" t="inlineStr">
         <is>
-          <t>알지노믹스</t>
+          <t>선익시스템  (신규)</t>
         </is>
       </c>
       <c r="B143" s="11" t="n">
         <v>9</v>
       </c>
       <c r="C143" s="11" t="n">
-        <v>87210062</v>
+        <v>315945223</v>
       </c>
       <c r="D143" s="12" t="inlineStr">
         <is>
-          <t>0.75%→1.04%</t>
+          <t>0.00%→1.13%</t>
         </is>
       </c>
       <c r="E143" s="13" t="inlineStr">
         <is>
-          <t>21→30</t>
+          <t>0→9</t>
         </is>
       </c>
       <c r="G143" s="14" t="inlineStr">
@@ -5643,23 +5643,23 @@
       <c r="E147" s="17" t="n"/>
       <c r="G147" s="14" t="inlineStr">
         <is>
-          <t>서진시스템</t>
+          <t>오이솔루션</t>
         </is>
       </c>
       <c r="H147" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I147" s="15" t="n">
-        <v>-93266316</v>
+        <v>-71400050</v>
       </c>
       <c r="J147" s="16" t="inlineStr">
         <is>
-          <t>4.02%→3.58%</t>
+          <t>1.05%→0.77%</t>
         </is>
       </c>
       <c r="K147" s="13" t="inlineStr">
         <is>
-          <t>82→75</t>
+          <t>28→21</t>
         </is>
       </c>
     </row>
@@ -5671,23 +5671,23 @@
       <c r="E148" s="17" t="n"/>
       <c r="G148" s="14" t="inlineStr">
         <is>
-          <t>오이솔루션</t>
+          <t>서진시스템</t>
         </is>
       </c>
       <c r="H148" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I148" s="15" t="n">
-        <v>-71400050</v>
+        <v>-93266316</v>
       </c>
       <c r="J148" s="16" t="inlineStr">
         <is>
-          <t>1.05%→0.77%</t>
+          <t>4.02%→3.58%</t>
         </is>
       </c>
       <c r="K148" s="13" t="inlineStr">
         <is>
-          <t>28→21</t>
+          <t>82→75</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_rolling5_20261027.xlsx
+++ b/reports/pdf_rolling5_20261027.xlsx
@@ -1186,23 +1186,23 @@
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>원익머트리얼즈</t>
+          <t>파두</t>
         </is>
       </c>
       <c r="B18" s="11" t="n">
         <v>12</v>
       </c>
       <c r="C18" s="11" t="n">
-        <v>393228055</v>
+        <v>533836875</v>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>1.43%→1.47%</t>
+          <t>0.42%→0.50%</t>
         </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
-          <t>173→185</t>
+          <t>34→46</t>
         </is>
       </c>
       <c r="G18" s="17" t="n"/>
@@ -1242,23 +1242,23 @@
     <row r="20">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>파두</t>
+          <t>원익머트리얼즈</t>
         </is>
       </c>
       <c r="B20" s="11" t="n">
         <v>12</v>
       </c>
       <c r="C20" s="11" t="n">
-        <v>533836875</v>
+        <v>393228055</v>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
-          <t>0.42%→0.50%</t>
+          <t>1.43%→1.47%</t>
         </is>
       </c>
       <c r="E20" s="13" t="inlineStr">
         <is>
-          <t>34→46</t>
+          <t>173→185</t>
         </is>
       </c>
       <c r="G20" s="17" t="n"/>
@@ -1828,23 +1828,23 @@
       <c r="E37" s="17" t="n"/>
       <c r="G37" s="14" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>에스티팜</t>
         </is>
       </c>
       <c r="H37" s="15" t="n">
         <v>-22</v>
       </c>
       <c r="I37" s="15" t="n">
-        <v>-2711311990</v>
+        <v>-1045538611</v>
       </c>
       <c r="J37" s="16" t="inlineStr">
         <is>
-          <t>3.83%→2.48%</t>
+          <t>7.45%→7.13%</t>
         </is>
       </c>
       <c r="K37" s="13" t="inlineStr">
         <is>
-          <t>81→59</t>
+          <t>462→440</t>
         </is>
       </c>
     </row>
@@ -1856,23 +1856,23 @@
       <c r="E38" s="17" t="n"/>
       <c r="G38" s="14" t="inlineStr">
         <is>
-          <t>에스티팜</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="H38" s="15" t="n">
         <v>-22</v>
       </c>
       <c r="I38" s="15" t="n">
-        <v>-1045538611</v>
+        <v>-2711311990</v>
       </c>
       <c r="J38" s="16" t="inlineStr">
         <is>
-          <t>7.45%→7.13%</t>
+          <t>3.83%→2.48%</t>
         </is>
       </c>
       <c r="K38" s="13" t="inlineStr">
         <is>
-          <t>462→440</t>
+          <t>81→59</t>
         </is>
       </c>
     </row>
@@ -2321,23 +2321,23 @@
       </c>
       <c r="G52" s="14" t="inlineStr">
         <is>
-          <t>필옵틱스</t>
+          <t>한선엔지니어링</t>
         </is>
       </c>
       <c r="H52" s="15" t="n">
         <v>-112</v>
       </c>
       <c r="I52" s="15" t="n">
-        <v>-2061201705</v>
+        <v>-948301072</v>
       </c>
       <c r="J52" s="16" t="inlineStr">
         <is>
-          <t>2.12%→1.00%</t>
+          <t>1.01%→0.43%</t>
         </is>
       </c>
       <c r="K52" s="13" t="inlineStr">
         <is>
-          <t>220→108</t>
+          <t>213→101</t>
         </is>
       </c>
     </row>
@@ -2365,23 +2365,23 @@
       </c>
       <c r="G53" s="14" t="inlineStr">
         <is>
-          <t>한선엔지니어링</t>
+          <t>필옵틱스</t>
         </is>
       </c>
       <c r="H53" s="15" t="n">
         <v>-112</v>
       </c>
       <c r="I53" s="15" t="n">
-        <v>-948301072</v>
+        <v>-2061201705</v>
       </c>
       <c r="J53" s="16" t="inlineStr">
         <is>
-          <t>1.01%→0.43%</t>
+          <t>2.12%→1.00%</t>
         </is>
       </c>
       <c r="K53" s="13" t="inlineStr">
         <is>
-          <t>213→101</t>
+          <t>220→108</t>
         </is>
       </c>
     </row>
@@ -2520,18 +2520,18 @@
     <row r="57">
       <c r="A57" s="10" t="inlineStr">
         <is>
-          <t>디케이티  (신규)</t>
+          <t>엘티씨  (신규)</t>
         </is>
       </c>
       <c r="B57" s="11" t="n">
         <v>99</v>
       </c>
       <c r="C57" s="11" t="n">
-        <v>1612233631</v>
+        <v>2103768275</v>
       </c>
       <c r="D57" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.81%</t>
+          <t>0.00%→1.06%</t>
         </is>
       </c>
       <c r="E57" s="13" t="inlineStr">
@@ -2564,18 +2564,18 @@
     <row r="58">
       <c r="A58" s="10" t="inlineStr">
         <is>
-          <t>엘티씨  (신규)</t>
+          <t>디케이티  (신규)</t>
         </is>
       </c>
       <c r="B58" s="11" t="n">
         <v>99</v>
       </c>
       <c r="C58" s="11" t="n">
-        <v>2103768275</v>
+        <v>1612233631</v>
       </c>
       <c r="D58" s="12" t="inlineStr">
         <is>
-          <t>0.00%→1.06%</t>
+          <t>0.00%→0.81%</t>
         </is>
       </c>
       <c r="E58" s="13" t="inlineStr">
@@ -2981,23 +2981,23 @@
       </c>
       <c r="G67" s="14" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>대주전자재료</t>
         </is>
       </c>
       <c r="H67" s="15" t="n">
         <v>-26</v>
       </c>
       <c r="I67" s="15" t="n">
-        <v>-4148088992</v>
+        <v>-1580060454</v>
       </c>
       <c r="J67" s="16" t="inlineStr">
         <is>
-          <t>4.69%→2.73%</t>
+          <t>1.57%→0.73%</t>
         </is>
       </c>
       <c r="K67" s="13" t="inlineStr">
         <is>
-          <t>60→34</t>
+          <t>50→24</t>
         </is>
       </c>
     </row>
@@ -3009,23 +3009,23 @@
       <c r="E68" s="17" t="n"/>
       <c r="G68" s="14" t="inlineStr">
         <is>
-          <t>대주전자재료</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="H68" s="15" t="n">
         <v>-26</v>
       </c>
       <c r="I68" s="15" t="n">
-        <v>-1580060454</v>
+        <v>-4148088992</v>
       </c>
       <c r="J68" s="16" t="inlineStr">
         <is>
-          <t>1.57%→0.73%</t>
+          <t>4.69%→2.73%</t>
         </is>
       </c>
       <c r="K68" s="13" t="inlineStr">
         <is>
-          <t>50→24</t>
+          <t>60→34</t>
         </is>
       </c>
     </row>
@@ -3037,23 +3037,23 @@
       <c r="E69" s="17" t="n"/>
       <c r="G69" s="14" t="inlineStr">
         <is>
-          <t>에이비엘바이오  (편출)</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="H69" s="15" t="n">
         <v>-25</v>
       </c>
       <c r="I69" s="15" t="n">
-        <v>-772056940</v>
+        <v>-1074094221</v>
       </c>
       <c r="J69" s="16" t="inlineStr">
         <is>
-          <t>0.33%→0.00%</t>
+          <t>1.19%→0.76%</t>
         </is>
       </c>
       <c r="K69" s="13" t="inlineStr">
         <is>
-          <t>25→0</t>
+          <t>60→35</t>
         </is>
       </c>
     </row>
@@ -3065,23 +3065,23 @@
       <c r="E70" s="17" t="n"/>
       <c r="G70" s="14" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>에이비엘바이오  (편출)</t>
         </is>
       </c>
       <c r="H70" s="15" t="n">
         <v>-25</v>
       </c>
       <c r="I70" s="15" t="n">
-        <v>-1074094221</v>
+        <v>-772056940</v>
       </c>
       <c r="J70" s="16" t="inlineStr">
         <is>
-          <t>1.19%→0.76%</t>
+          <t>0.33%→0.00%</t>
         </is>
       </c>
       <c r="K70" s="13" t="inlineStr">
         <is>
-          <t>60→35</t>
+          <t>25→0</t>
         </is>
       </c>
     </row>
@@ -4030,23 +4030,23 @@
     <row r="100">
       <c r="A100" s="10" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>나노신소재</t>
         </is>
       </c>
       <c r="B100" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C100" s="11" t="n">
-        <v>34329600</v>
+        <v>21235200</v>
       </c>
       <c r="D100" s="12" t="inlineStr">
         <is>
-          <t>1.80%→1.94%</t>
+          <t>0.12%→0.22%</t>
         </is>
       </c>
       <c r="E100" s="13" t="inlineStr">
         <is>
-          <t>72→78</t>
+          <t>8→14</t>
         </is>
       </c>
       <c r="G100" s="17" t="n"/>
@@ -4058,23 +4058,23 @@
     <row r="101">
       <c r="A101" s="10" t="inlineStr">
         <is>
-          <t>나노신소재</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="B101" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C101" s="11" t="n">
-        <v>21235200</v>
+        <v>34329600</v>
       </c>
       <c r="D101" s="12" t="inlineStr">
         <is>
-          <t>0.12%→0.22%</t>
+          <t>1.80%→1.94%</t>
         </is>
       </c>
       <c r="E101" s="13" t="inlineStr">
         <is>
-          <t>8→14</t>
+          <t>72→78</t>
         </is>
       </c>
       <c r="G101" s="17" t="n"/>
@@ -5074,23 +5074,23 @@
       <c r="E131" s="17" t="n"/>
       <c r="G131" s="14" t="inlineStr">
         <is>
-          <t>이오테크닉스</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="H131" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I131" s="15" t="n">
-        <v>-254688121</v>
+        <v>-161952077</v>
       </c>
       <c r="J131" s="16" t="inlineStr">
         <is>
-          <t>4.42%→3.92%</t>
+          <t>2.45%→2.13%</t>
         </is>
       </c>
       <c r="K131" s="13" t="inlineStr">
         <is>
-          <t>53→49</t>
+          <t>46→42</t>
         </is>
       </c>
     </row>
@@ -5102,23 +5102,23 @@
       <c r="E132" s="17" t="n"/>
       <c r="G132" s="14" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>이오테크닉스</t>
         </is>
       </c>
       <c r="H132" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I132" s="15" t="n">
-        <v>-161952077</v>
+        <v>-254688121</v>
       </c>
       <c r="J132" s="16" t="inlineStr">
         <is>
-          <t>2.45%→2.13%</t>
+          <t>4.42%→3.92%</t>
         </is>
       </c>
       <c r="K132" s="13" t="inlineStr">
         <is>
-          <t>46→42</t>
+          <t>53→49</t>
         </is>
       </c>
     </row>
@@ -5279,23 +5279,23 @@
       </c>
       <c r="G138" s="14" t="inlineStr">
         <is>
-          <t>덕산하이메탈</t>
+          <t>피엠티</t>
         </is>
       </c>
       <c r="H138" s="15" t="n">
         <v>-50</v>
       </c>
       <c r="I138" s="15" t="n">
-        <v>-216325153</v>
+        <v>-67468798</v>
       </c>
       <c r="J138" s="16" t="inlineStr">
         <is>
-          <t>1.43%→0.62%</t>
+          <t>0.26%→0.01%</t>
         </is>
       </c>
       <c r="K138" s="13" t="inlineStr">
         <is>
-          <t>90→40</t>
+          <t>53→3</t>
         </is>
       </c>
     </row>
@@ -5323,23 +5323,23 @@
       </c>
       <c r="G139" s="14" t="inlineStr">
         <is>
-          <t>피엠티</t>
+          <t>덕산하이메탈</t>
         </is>
       </c>
       <c r="H139" s="15" t="n">
         <v>-50</v>
       </c>
       <c r="I139" s="15" t="n">
-        <v>-67468798</v>
+        <v>-216325153</v>
       </c>
       <c r="J139" s="16" t="inlineStr">
         <is>
-          <t>0.26%→0.01%</t>
+          <t>1.43%→0.62%</t>
         </is>
       </c>
       <c r="K139" s="13" t="inlineStr">
         <is>
-          <t>53→3</t>
+          <t>90→40</t>
         </is>
       </c>
     </row>
@@ -5434,23 +5434,23 @@
     <row r="142">
       <c r="A142" s="10" t="inlineStr">
         <is>
-          <t>알지노믹스</t>
+          <t>선익시스템  (신규)</t>
         </is>
       </c>
       <c r="B142" s="11" t="n">
         <v>9</v>
       </c>
       <c r="C142" s="11" t="n">
-        <v>87210062</v>
+        <v>315945223</v>
       </c>
       <c r="D142" s="12" t="inlineStr">
         <is>
-          <t>0.75%→1.04%</t>
+          <t>0.00%→1.13%</t>
         </is>
       </c>
       <c r="E142" s="13" t="inlineStr">
         <is>
-          <t>21→30</t>
+          <t>0→9</t>
         </is>
       </c>
       <c r="G142" s="14" t="inlineStr">
@@ -5478,23 +5478,23 @@
     <row r="143">
       <c r="A143" s="10" t="inlineStr">
         <is>
-          <t>선익시스템  (신규)</t>
+          <t>알지노믹스</t>
         </is>
       </c>
       <c r="B143" s="11" t="n">
         <v>9</v>
       </c>
       <c r="C143" s="11" t="n">
-        <v>315945223</v>
+        <v>87210062</v>
       </c>
       <c r="D143" s="12" t="inlineStr">
         <is>
-          <t>0.00%→1.13%</t>
+          <t>0.75%→1.04%</t>
         </is>
       </c>
       <c r="E143" s="13" t="inlineStr">
         <is>
-          <t>0→9</t>
+          <t>21→30</t>
         </is>
       </c>
       <c r="G143" s="14" t="inlineStr">
@@ -5643,23 +5643,23 @@
       <c r="E147" s="17" t="n"/>
       <c r="G147" s="14" t="inlineStr">
         <is>
-          <t>오이솔루션</t>
+          <t>서진시스템</t>
         </is>
       </c>
       <c r="H147" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I147" s="15" t="n">
-        <v>-71400050</v>
+        <v>-93266316</v>
       </c>
       <c r="J147" s="16" t="inlineStr">
         <is>
-          <t>1.05%→0.77%</t>
+          <t>4.02%→3.58%</t>
         </is>
       </c>
       <c r="K147" s="13" t="inlineStr">
         <is>
-          <t>28→21</t>
+          <t>82→75</t>
         </is>
       </c>
     </row>
@@ -5671,23 +5671,23 @@
       <c r="E148" s="17" t="n"/>
       <c r="G148" s="14" t="inlineStr">
         <is>
-          <t>서진시스템</t>
+          <t>오이솔루션</t>
         </is>
       </c>
       <c r="H148" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I148" s="15" t="n">
-        <v>-93266316</v>
+        <v>-71400050</v>
       </c>
       <c r="J148" s="16" t="inlineStr">
         <is>
-          <t>4.02%→3.58%</t>
+          <t>1.05%→0.77%</t>
         </is>
       </c>
       <c r="K148" s="13" t="inlineStr">
         <is>
-          <t>82→75</t>
+          <t>28→21</t>
         </is>
       </c>
     </row>
